--- a/Master_TestCases.xlsx
+++ b/Master_TestCases.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M137"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -554,10 +554,10 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K4">
-        <v>928</v>
+        <v>1733</v>
       </c>
       <c r="L4" t="str">
         <v/>
@@ -595,10 +595,10 @@
         <v>expectSuccessStatus on response | Content-Type contains application/json | expectAuthLoginOtpSuccessBody: success=true, statusCode=200, message = OTP required. | Non-empty: data.loginAttemptId, data.methods, data.methods[0].type, data.expiresInSeconds | Some method has type === "EMAIL"</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K5">
-        <v>597</v>
+        <v>709</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -636,10 +636,10 @@
         <v>expectHttpStatus 401 | JSON Content-Type | expectAuthInvalidCredentialsBody: success=false, statusCode=401, error.code = UNAUTHORIZED, message = Incorrect email or password.</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K6">
-        <v>1039</v>
+        <v>1875</v>
       </c>
       <c r="L6" t="str">
         <v/>
@@ -677,10 +677,10 @@
         <v>Same as AUTH-LOGIN-002</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K7">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="L7" t="str">
         <v/>
@@ -718,10 +718,10 @@
         <v>expectHttpStatus 422 | JSON Content-Type | expectAuthValidationErrorBody with detailsField email: VALIDATION_ERROR envelope, non-empty error.details, row for email</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K8">
-        <v>495</v>
+        <v>353</v>
       </c>
       <c r="L8" t="str">
         <v/>
@@ -759,10 +759,10 @@
         <v>Same as AUTH-LOGIN-004 pattern with password in details</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K9">
-        <v>289</v>
+        <v>339</v>
       </c>
       <c r="L9" t="str">
         <v/>
@@ -800,10 +800,10 @@
         <v>expectAuthValidationErrorBody (VALIDATION_ERROR + non-empty details; no single field pinned)</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K10">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="L10" t="str">
         <v/>
@@ -841,10 +841,10 @@
         <v>Same as AUTH-LOGIN-006</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K11">
-        <v>233</v>
+        <v>313</v>
       </c>
       <c r="L11" t="str">
         <v/>
@@ -882,10 +882,10 @@
         <v>Same success path as AUTH-LOGIN-001 (expectSuccessStatus, expectJsonContentType, expectAuthLoginOtpSuccessBody)</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K12">
-        <v>231</v>
+        <v>302</v>
       </c>
       <c r="L12" t="str" xml:space="preserve">
         <v xml:space="preserve">Error: Expected 2xx, got HTTP 422 — Validation failed.
@@ -925,10 +925,10 @@
         <v>Same as AUTH-LOGIN-001</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K13">
-        <v>1163</v>
+        <v>1086</v>
       </c>
       <c r="L13" t="str">
         <v/>
@@ -966,10 +966,10 @@
         <v>Same as AUTH-LOGIN-001</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K14">
-        <v>565</v>
+        <v>845</v>
       </c>
       <c r="L14" t="str">
         <v/>
@@ -1007,10 +1007,10 @@
         <v>Same as AUTH-LOGIN-001</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K15">
-        <v>808</v>
+        <v>730</v>
       </c>
       <c r="L15" t="str">
         <v/>
@@ -1048,10 +1048,10 @@
         <v>Same as AUTH-LOGIN-002</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K16">
-        <v>831</v>
+        <v>464</v>
       </c>
       <c r="L16" t="str">
         <v/>
@@ -1089,10 +1089,10 @@
         <v>Same as AUTH-LOGIN-002</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K17">
-        <v>328</v>
+        <v>312</v>
       </c>
       <c r="L17" t="str">
         <v/>
@@ -1130,10 +1130,10 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K18">
-        <v>946</v>
+        <v>1666</v>
       </c>
       <c r="L18" t="str">
         <v/>
@@ -1171,10 +1171,10 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K19">
-        <v>280</v>
+        <v>363</v>
       </c>
       <c r="L19" t="str">
         <v/>
@@ -1253,10 +1253,10 @@
         <v>Prior steps: login / send / verify asserted with auth helpers | Refresh: expectSuccessStatus, JSON type, expectAuthRefreshSuccessBody (Token refreshed., non-empty access + refresh tokens, tokenType, expiresInSeconds)</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K21">
-        <v>2631</v>
+        <v>3117</v>
       </c>
       <c r="L21" t="str">
         <v/>
@@ -1294,10 +1294,10 @@
         <v>expectHttpStatus 401; JSON; expectAuthRefreshInvalidBody (UNAUTHORIZED, Authentication required., AUTH_REFRESH_INVALID)</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K22">
-        <v>877</v>
+        <v>1612</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -1335,10 +1335,10 @@
         <v>Same as AUTH-REFRESH-002</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K23">
-        <v>286</v>
+        <v>404</v>
       </c>
       <c r="L23" t="str">
         <v/>
@@ -1376,10 +1376,10 @@
         <v>Same as AUTH-REFRESH-002</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K24">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="L24" t="str">
         <v/>
@@ -1417,10 +1417,10 @@
         <v>First response expectAuthRefreshSuccessBody; second same invalid body as AUTH-REFRESH-002</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K25">
-        <v>2891</v>
+        <v>3348</v>
       </c>
       <c r="L25" t="str">
         <v/>
@@ -1458,10 +1458,10 @@
         <v>expectAuthRefreshSuccessBody; new data.refreshToken ≠ token from verify response</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K26">
-        <v>2670</v>
+        <v>3096</v>
       </c>
       <c r="L26" t="str">
         <v/>
@@ -1499,10 +1499,10 @@
         <v>On success: same refresh success body as AUTH-REFRESH-001</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K27">
-        <v>2502</v>
+        <v>2472</v>
       </c>
       <c r="L27" t="str">
         <v/>
@@ -1540,10 +1540,10 @@
         <v>Same as AUTH-REFRESH-002</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K28">
-        <v>265</v>
+        <v>353</v>
       </c>
       <c r="L28" t="str">
         <v/>
@@ -1581,10 +1581,10 @@
         <v>Login: expectSuccessStatus, JSON type, expectAuthLoginOtpSuccessBody | Send-otp: expectSuccessStatus, JSON type, expectAuthSendOtpSuccessBody (OTP generated., non-empty data.delivery.type, data.delivery.masked, data.expiresInSeconds)</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K29">
-        <v>893</v>
+        <v>803</v>
       </c>
       <c r="L29" t="str">
         <v/>
@@ -1622,10 +1622,10 @@
         <v>expectHttpStatus 422 | JSON Content-Type | expectAuthSendOtpValidationErrorBody with loginAttemptId in error.details</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K30">
-        <v>921</v>
+        <v>1506</v>
       </c>
       <c r="L30" t="str">
         <v/>
@@ -1663,10 +1663,10 @@
         <v>Same validation helper; non-empty details (no field pin in call)</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K31">
-        <v>282</v>
+        <v>410</v>
       </c>
       <c r="L31" t="str">
         <v/>
@@ -1704,10 +1704,10 @@
         <v>expectHttpStatus 400 | JSON Content-Type | expectAuthSendOtpBadRequestBody: BAD_REQUEST, message = Only EMAIL is supported for now., error.key = AUTH_FORBIDDEN</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K32">
-        <v>1167</v>
+        <v>1012</v>
       </c>
       <c r="L32" t="str">
         <v/>
@@ -1745,10 +1745,10 @@
         <v>BAD_REQUEST, message = Invalid loginAttemptId., error.key = AUTH_FORBIDDEN</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K33">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c r="L33" t="str">
         <v/>
@@ -1786,10 +1786,10 @@
         <v>Login OTP body + send-otp success body (same as AUTH-SENDOTP-001 send step)</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K34">
-        <v>677</v>
+        <v>767</v>
       </c>
       <c r="L34" t="str">
         <v/>
@@ -1827,10 +1827,10 @@
         <v>Same as AUTH-SENDOTP-004</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K35">
-        <v>1204</v>
+        <v>784</v>
       </c>
       <c r="L35" t="str">
         <v/>
@@ -1868,10 +1868,10 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K36">
-        <v>823</v>
+        <v>1593</v>
       </c>
       <c r="L36" t="str">
         <v/>
@@ -1909,10 +1909,10 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K37">
-        <v>252</v>
+        <v>367</v>
       </c>
       <c r="L37" t="str">
         <v/>
@@ -1991,10 +1991,10 @@
         <v>Login + send-otp: success + auth helpers as in other specs | Verify: expectSuccessStatus, JSON type, expectAuthVerifyOtpSuccessBody (Login successful., tokens, data.account.id, data.org.id, data.org.orgUserId, data.org.orgRole, expiry fields)</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K39">
-        <v>1553</v>
+        <v>1933</v>
       </c>
       <c r="L39" t="str">
         <v/>
@@ -2032,10 +2032,10 @@
         <v>expectHttpStatus 400; JSON; expectAuthVerifyOtpBadRequestBody — BAD_REQUEST, OTP not generated yet., error.key AUTH_FORBIDDEN</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K40">
-        <v>872</v>
+        <v>799</v>
       </c>
       <c r="L40" t="str">
         <v/>
@@ -2073,10 +2073,10 @@
         <v>expectAuthVerifyOtpInvalidOtpBody — UNAUTHORIZED, Invalid OTP., error.key AUTH_INVALID_CREDENTIALS</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K41">
-        <v>1154</v>
+        <v>1266</v>
       </c>
       <c r="L41" t="str">
         <v/>
@@ -2114,10 +2114,10 @@
         <v>expectAuthVerifyOtpValidationErrorBody with loginAttemptId in details</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K42">
-        <v>290</v>
+        <v>328</v>
       </c>
       <c r="L42" t="str">
         <v/>
@@ -2155,10 +2155,10 @@
         <v>expectAuthVerifyOtpValidationErrorBody with otp in details</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K43">
-        <v>1032</v>
+        <v>1199</v>
       </c>
       <c r="L43" t="str">
         <v/>
@@ -2196,10 +2196,10 @@
         <v>expectAuthVerifyOtpBadRequestBody — OTP already used. Please login again., AUTH_FORBIDDEN</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K44">
-        <v>1651</v>
+        <v>2334</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
         <v>Same as AUTH-VERIFY-001 verify step; optional note on Set-Cookie (not asserted)</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K45">
-        <v>1969</v>
+        <v>1867</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2278,10 +2278,10 @@
         <v>Same as AUTH-VERIFY-002</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K46">
-        <v>1152</v>
+        <v>1102</v>
       </c>
       <c r="L46" t="str">
         <v/>
@@ -2319,10 +2319,10 @@
         <v>Same as AUTH-VERIFY-003</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K47">
-        <v>1237</v>
+        <v>1330</v>
       </c>
       <c r="L47" t="str">
         <v/>
@@ -2360,10 +2360,10 @@
         <v>Same as AUTH-VERIFY-006</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K48">
-        <v>1808</v>
+        <v>2660</v>
       </c>
       <c r="L48" t="str">
         <v/>
@@ -2401,10 +2401,10 @@
         <v>Same as AUTH-VERIFY-001 verify body | data.org.orgRole === "MEMBER" | data.branch present; data.branch.id non-empty string</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K49">
-        <v>1684</v>
+        <v>1917</v>
       </c>
       <c r="L49" t="str">
         <v/>
@@ -2442,10 +2442,10 @@
         <v>expectHttpStatus 401 | JSON Content-Type | Body truthy | expectJsonErrorBody — statusCode 401, message contains Authentication, non-empty error.code and error.key</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K50">
-        <v>267</v>
+        <v>297</v>
       </c>
       <c r="L50" t="str">
         <v/>
@@ -2483,10 +2483,10 @@
         <v>expectOrgUserCreateSuccessBody — message contains User created (e.g. User created. or invitation-sent variant), data.orgUserId</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K51">
-        <v>2224</v>
+        <v>2433</v>
       </c>
       <c r="L51" t="str">
         <v/>
@@ -2524,10 +2524,10 @@
         <v>expectJsonErrorBody (Authentication, error code/key)</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K52">
-        <v>263</v>
+        <v>300</v>
       </c>
       <c r="L52" t="str">
         <v/>
@@ -2565,10 +2565,10 @@
         <v>expectAuthValidationErrorBody — field email</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K53">
-        <v>2203</v>
+        <v>2025</v>
       </c>
       <c r="L53" t="str">
         <v/>
@@ -2606,10 +2606,10 @@
         <v>loginWithOtp as employee; POST create; expectNonSuccess; status in {401,403}</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K54">
-        <v>2488</v>
+        <v>2201</v>
       </c>
       <c r="L54" t="str">
         <v/>
@@ -2647,10 +2647,10 @@
         <v>branchId === session.branchId; expectOrgUserCreateSuccessBody</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K55">
-        <v>1726</v>
+        <v>2084</v>
       </c>
       <c r="L55" t="str">
         <v/>
@@ -2688,10 +2688,10 @@
         <v>Skips if wrong branch equals supervisor branch; success === false</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K56">
-        <v>1982</v>
+        <v>2370</v>
       </c>
       <c r="L56" t="str">
         <v/>
@@ -2729,10 +2729,10 @@
         <v>overrides.branchRole = SUPERVISOR; success === false</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K57">
-        <v>1602</v>
+        <v>1741</v>
       </c>
       <c r="L57" t="str">
         <v/>
@@ -2770,10 +2770,10 @@
         <v>Second response not OK; success === false</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K58">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="L58" t="str">
         <v/>
@@ -2811,10 +2811,10 @@
         <v>Fake UUID in departmentIds; success === false</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K59">
-        <v>1393</v>
+        <v>1952</v>
       </c>
       <c r="L59" t="str">
         <v/>
@@ -2852,10 +2852,10 @@
         <v>Non-existent UUID; success === false</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K60">
-        <v>1565</v>
+        <v>2251</v>
       </c>
       <c r="L60" t="str">
         <v/>
@@ -2893,10 +2893,10 @@
         <v>paymentMethod, baseWage in payload; success === false</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K61">
-        <v>1776</v>
+        <v>1555</v>
       </c>
       <c r="L61" t="str">
         <v/>
@@ -2975,10 +2975,10 @@
         <v>Error envelope shape with success=false, statusCode, error.code, error.key</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K63">
-        <v>1773</v>
+        <v>2297</v>
       </c>
       <c r="L63" t="str">
         <v/>
@@ -3016,10 +3016,10 @@
         <v>Error envelope shape with success=false, statusCode, error.code, error.key</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K64">
-        <v>1887</v>
+        <v>2154</v>
       </c>
       <c r="L64" t="str">
         <v/>
@@ -3057,10 +3057,10 @@
         <v>Error envelope shape with success=false, statusCode, error.code, error.key</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K65">
-        <v>3138</v>
+        <v>3657</v>
       </c>
       <c r="L65" t="str">
         <v/>
@@ -3098,10 +3098,10 @@
         <v>Create request fails when required fields are removed from payload</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K66">
-        <v>1795</v>
+        <v>1822</v>
       </c>
       <c r="L66" t="str">
         <v/>
@@ -3139,10 +3139,10 @@
         <v>loginWithOtp (supervisor); session has branchId | expectSuccessStatus, JSON type | expectOrgUsersOptionsSuccessBody — success 200; options array from data / data.items / data.options | Each row: non-empty orgUserId, fullName, email, branchRole | Each branchRole is EMPLOYEE or SUPERVISOR only</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K67">
-        <v>5201</v>
+        <v>4835</v>
       </c>
       <c r="L67" t="str">
         <v/>
@@ -3180,10 +3180,10 @@
         <v>expectJsonErrorBody — 401, message contains Authentication, non-empty error.code and error.key</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K68">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="L68" t="str">
         <v/>
@@ -3221,10 +3221,10 @@
         <v>Same options body contract as ORGS-OPTS-001</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K69">
-        <v>3817</v>
+        <v>5336</v>
       </c>
       <c r="L69" t="str">
         <v/>
@@ -3262,10 +3262,10 @@
         <v>Same options body contract as ORGS-OPTS-001</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K70">
-        <v>5002</v>
+        <v>4397</v>
       </c>
       <c r="L70" t="str">
         <v/>
@@ -3303,10 +3303,10 @@
         <v>Employee uses non-own branchId; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K71">
-        <v>4865</v>
+        <v>5891</v>
       </c>
       <c r="L71" t="str">
         <v/>
@@ -3344,10 +3344,10 @@
         <v>Supervisor uses non-own branchId; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K72">
-        <v>4441</v>
+        <v>4823</v>
       </c>
       <c r="L72" t="str">
         <v/>
@@ -3385,10 +3385,10 @@
         <v>expectOrgUserCreateSuccessBody | First GET: expectOrgUserGetSuccessBody, data.fullName equals create payload | expectOrgUserPatchSuccessBody — JSON statusCode 200 or 201 | Second GET: expectOrgUserGetSuccessBody, expectOrgUserDetailMatchesPatch on data vs patch payload (name, phone, status, employeeId, modules, departments when returned)</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K73">
-        <v>3812</v>
+        <v>3332</v>
       </c>
       <c r="L73" t="str">
         <v/>
@@ -3426,10 +3426,10 @@
         <v>Error envelope shape with success=false, statusCode, error.code, error.key</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K74">
-        <v>2155</v>
+        <v>2374</v>
       </c>
       <c r="L74" t="str">
         <v/>
@@ -3467,10 +3467,10 @@
         <v>Inactive user cannot obtain a new authenticated session; cleanup restores ACTIVE status</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K75">
-        <v>5373</v>
+        <v>4690</v>
       </c>
       <c r="L75" t="str">
         <v/>
@@ -3508,10 +3508,10 @@
         <v>Success envelope for PATCH update</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K76">
-        <v>2312</v>
+        <v>1977</v>
       </c>
       <c r="L76" t="str">
         <v/>
@@ -3549,10 +3549,10 @@
         <v>Success envelope for PATCH update</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K77">
-        <v>2347</v>
+        <v>1863</v>
       </c>
       <c r="L77" t="str">
         <v/>
@@ -3590,10 +3590,10 @@
         <v>Error envelope for forbidden supervisor update</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K78">
-        <v>1703</v>
+        <v>1708</v>
       </c>
       <c r="L78" t="str">
         <v/>
@@ -3631,10 +3631,10 @@
         <v>Error envelope for forbidden supervisor update</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K79">
-        <v>1613</v>
+        <v>1820</v>
       </c>
       <c r="L79" t="str">
         <v/>
@@ -3672,10 +3672,10 @@
         <v>Error envelope for forbidden supervisor update</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K80">
-        <v>1653</v>
+        <v>1713</v>
       </c>
       <c r="L80" t="str">
         <v/>
@@ -3713,10 +3713,10 @@
         <v>Error envelope for forbidden supervisor update</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K81">
-        <v>1581</v>
+        <v>1708</v>
       </c>
       <c r="L81" t="str">
         <v/>
@@ -3754,10 +3754,10 @@
         <v>Error envelope for forbidden supervisor update</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K82">
-        <v>1855</v>
+        <v>2410</v>
       </c>
       <c r="L82" t="str">
         <v/>
@@ -3836,10 +3836,10 @@
         <v>After loginWithOtp with owner email | expectSuccessStatus, JSON type | expectOrgUsersListSuccessBody — envelope 200, data.page / data.limit / data.total, non-empty items array, each row has identity</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K84">
-        <v>2313</v>
+        <v>2858</v>
       </c>
       <c r="L84" t="str">
         <v/>
@@ -3877,10 +3877,10 @@
         <v>JSON; expectJsonErrorBody — 401, message contains Authentication, non-empty error.code and error.key</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K85">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="L85" t="str">
         <v/>
@@ -3918,10 +3918,10 @@
         <v>Same list body as ORGS-USERS-001; data.total &gt;= 2</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K86">
-        <v>2806</v>
+        <v>2248</v>
       </c>
       <c r="L86" t="str">
         <v/>
@@ -3959,10 +3959,10 @@
         <v>Same list body helper | Every row listItemIdentity(row) equals session orgUserId | data.total === number of returned rows</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K87">
-        <v>1611</v>
+        <v>2856</v>
       </c>
       <c r="L87" t="str">
         <v/>
@@ -4000,10 +4000,10 @@
         <v>Same list body helper | If every row has branch id: single branch id equals session branchId | Else: listed identities include supervisor orgUserId</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K88">
-        <v>2075</v>
+        <v>2093</v>
       </c>
       <c r="L88" t="str">
         <v/>
@@ -4041,10 +4041,10 @@
         <v>On success, all rows must match employee self identity; otherwise error envelope is returned</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K89">
-        <v>2099</v>
+        <v>2154</v>
       </c>
       <c r="L89" t="str">
         <v/>
@@ -4082,10 +4082,10 @@
         <v>JSON error envelope with non-empty error.code</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K90">
-        <v>1876</v>
+        <v>2029</v>
       </c>
       <c r="L90" t="str">
         <v/>
@@ -4123,10 +4123,10 @@
         <v>List success envelope returned for search/filter query payload</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K91">
-        <v>1705</v>
+        <v>2261</v>
       </c>
       <c r="L91" t="str">
         <v/>
@@ -4164,10 +4164,10 @@
         <v>expectSuccessStatus, JSON type | expectOrgUserGetSuccessBody — envelope 200, data object, orgUserId (or id) matches session orgUserId</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K92">
-        <v>2475</v>
+        <v>2962</v>
       </c>
       <c r="L92" t="str">
         <v/>
@@ -4205,10 +4205,10 @@
         <v>expectJsonErrorBody — 401, message contains Authentication, non-empty error.code and error.key</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K93">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="L93" t="str">
         <v/>
@@ -4246,10 +4246,10 @@
         <v>Employee token attempts GET /orgs/:orgId/users/:orgUserId for a different user; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K94">
-        <v>4105</v>
+        <v>4561</v>
       </c>
       <c r="L94" t="str">
         <v/>
@@ -4287,10 +4287,10 @@
         <v>Supervisor token attempts GET /orgs/:orgId/users/:orgUserId for out-of-scope user; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K95">
-        <v>3248</v>
+        <v>4787</v>
       </c>
       <c r="L95" t="str">
         <v/>
@@ -4299,471 +4299,1749 @@
         <v>tests/api/regression/users.get.access.spec.js</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" xml:space="preserve">
       <c r="A96" t="str">
-        <v>TASKS-LIST-001</v>
+        <v>TASKS-ANALYTICS-001</v>
       </c>
       <c r="B96" t="str">
         <v>GET</v>
       </c>
       <c r="C96" t="str">
-        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+        <v>/orgs/:orgId/branches/:branchId/tasks/analytics</v>
       </c>
       <c r="D96" t="str">
-        <v>List tasks</v>
+        <v>Task analytics</v>
       </c>
       <c r="E96" t="str">
         <v>Smoke</v>
       </c>
       <c r="F96" t="str">
-        <v>Authorized owner lists tasks with pagination and filters</v>
+        <v>Authorized user fetches analytics for a bounded date range</v>
       </c>
       <c r="G96" t="str">
-        <v>HTTP 2xx, JSON</v>
+        <v>HTTP 2xx; JSON success envelope with data object</v>
       </c>
       <c r="H96" t="str">
-        <v>passed</v>
+        <v>failed</v>
       </c>
       <c r="I96" t="str">
-        <v>JWT via loginWithOtp (owner persona) | GET orgs/{orgId}/branches/{branchId}/tasks with page=1&amp;pageSize=20&amp;q=inventory&amp;sort=startAt&amp;order=asc | expectTasksListSuccessBody: | success=true, statusCode=200, string message | data is an array | pagination.type=offset | pagination.page&gt;=1, pagination.limit&gt;0 &amp;&amp; &lt;=100 | pagination.total&gt;=0, pagination.totalPages&gt;=1</v>
+        <v>GET .../tasks/analytics?from=...&amp;to=... | expectSuccessStatus, expectJsonSuccessBody, body.data is a non-null object</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K96">
-        <v>2031</v>
-      </c>
-      <c r="L96" t="str">
-        <v/>
+        <v>2921</v>
+      </c>
+      <c r="L96" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 400 — Task not found.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
       <c r="M96" t="str">
-        <v>tests/api/modules/tasks/smoke/tasks.list.spec.js</v>
+        <v>tests/api/modules/tasks/smoke/tasks.analytics.spec.js</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>TASKS-LIST-002</v>
+        <v>TASKS-BOARD-001</v>
       </c>
       <c r="B97" t="str">
         <v>GET</v>
       </c>
       <c r="C97" t="str">
-        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+        <v>/orgs/:orgId/branches/:branchId/tasks/board</v>
       </c>
       <c r="D97" t="str">
-        <v>List tasks</v>
+        <v>Task board</v>
       </c>
       <c r="E97" t="str">
         <v>Negative</v>
       </c>
       <c r="F97" t="str">
-        <v>Unauthorized tasks list request returns 401</v>
+        <v>Unauthorized board request returns 401</v>
       </c>
       <c r="G97" t="str">
-        <v>HTTP 401</v>
+        <v>HTTP 401; JSON error envelope</v>
       </c>
       <c r="H97" t="str">
         <v>passed</v>
       </c>
       <c r="I97" t="str">
-        <v>expectHttpStatus 401 | JSON Content-Type | expectJsonErrorBody: | statusCode=401 | message contains Authentication | non-empty error.code and error.key</v>
+        <v>GET orgs/{orgId}/branches/{branchId}/tasks/board without Authorization | expectHttpStatus 401 | expectJsonContentType | expectJsonErrorBody with statusCode=401, message contains Authentication, non-empty error.code and error.key</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
       <c r="K97">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="L97" t="str">
         <v/>
       </c>
       <c r="M97" t="str">
-        <v>tests/api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+        <v>tests/api/modules/tasks/negative/tasks.board.negative.spec.js</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>TASKS-LIST-003</v>
+        <v>TASKS-BOARD-002</v>
       </c>
       <c r="B98" t="str">
         <v>GET</v>
       </c>
       <c r="C98" t="str">
-        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+        <v>/orgs/:orgId/branches/:branchId/tasks/board</v>
       </c>
       <c r="D98" t="str">
-        <v>List tasks access by role</v>
+        <v>List tasks</v>
       </c>
       <c r="E98" t="str">
-        <v>Regression</v>
+        <v>Smoke</v>
       </c>
       <c r="F98" t="str">
-        <v>Owner branch tasks list returns successfully</v>
+        <v>Board view request with all supported query parameters returns successfully</v>
       </c>
       <c r="G98" t="str">
-        <v>HTTP 2xx</v>
+        <v>HTTP 2xx; JSON success envelope with board columns</v>
       </c>
       <c r="H98" t="str">
-        <v>passed</v>
+        <v/>
       </c>
       <c r="I98" t="str">
-        <v>expectTasksListSuccessBody with owner JWT and TASKS_BRANCH_ID</v>
+        <v>Use discovered valid IDs from initial board fetch (assigneeId, priorityId) and title snippet for q | GET orgs/{orgId}/branches/{branchId}/tasks/board with q, assigneeId, priorityId, includeSubtasks | expectSuccessStatus, expectJsonContentType, expectJsonSuccessBody with non-empty data.columns</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K98">
-        <v>2785</v>
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
       </c>
       <c r="L98" t="str">
         <v/>
       </c>
       <c r="M98" t="str">
-        <v>tests/api/regression/tasks.list.access.spec.js</v>
+        <v>tests/api/modules/tasks/smoke/tasks.boardview.spec.js</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>TASKS-LIST-004</v>
+        <v>TASKS-COMMENTS-001</v>
       </c>
       <c r="B99" t="str">
         <v>GET</v>
       </c>
       <c r="C99" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId/comments</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Task comments</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Authorized user lists comments for a task taken from the board</v>
+      </c>
+      <c r="G99" t="str">
+        <v>HTTP 2xx; JSON success envelope with data array</v>
+      </c>
+      <c r="H99" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Resolve taskId from GET .../tasks/board | GET .../tasks/{taskId}/comments?page=1&amp;limit=20 | expectSuccessStatus, expectJsonSuccessBody, Array.isArray(body.data)</v>
+      </c>
+      <c r="J99" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K99">
+        <v>2870</v>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.comments.spec.js</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>TASKS-DELETE-001</v>
+      </c>
+      <c r="B100" t="str">
+        <v>DELETE</v>
+      </c>
+      <c r="C100" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D100" t="str">
+        <v>Tasks CRUD</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Authorized user deletes the task created in the same serial suite</v>
+      </c>
+      <c r="G100" t="str">
+        <v>HTTP 2xx; JSON success envelope referencing deleted task</v>
+      </c>
+      <c r="H100" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I100" t="str">
+        <v>DELETE orgs/{orgId}/branches/{branchId}/tasks/{taskId} | expectSuccessStatus, expectJsonSuccessBody with messageIncludes deleted, data.taskId present</v>
+      </c>
+      <c r="J100" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K100">
+        <v>310</v>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>TASKS-DETAIL-001</v>
+      </c>
+      <c r="B101" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C101" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Task detail</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Task detail strict shape validation includes all expected sections</v>
+      </c>
+      <c r="G101" t="str">
+        <v>HTTP 2xx; JSON success envelope with expected task detail structure</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v>Preload board to pick a valid taskId | Validate status, priority, assignee, startAt, endAt | Validate reminders[], recurrence (object or null), attachments[], subtasks[], comments[], activityLogs[]</v>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.detail.spec.js</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>TASKS-DETAIL-002</v>
+      </c>
+      <c r="B102" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C102" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Task detail</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Unknown task id returns 404 not found</v>
+      </c>
+      <c r="G102" t="str">
+        <v>HTTP 404; JSON error envelope</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v>GET orgs/{orgId}/branches/{branchId}/tasks/{unknownTaskId} with valid JWT | expectHttpStatus 404 | expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.detail.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>TASKS-DETAIL-003</v>
+      </c>
+      <c r="B103" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C103" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Task detail</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Missing JWT on task detail endpoint returns unauthorized</v>
+      </c>
+      <c r="G103" t="str">
+        <v>HTTP 401; JSON error envelope</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v>GET orgs/{orgId}/branches/{branchId}/tasks/{taskId} without Authorization | expectHttpStatus 401 | expectJsonErrorBody with authentication message and non-empty error.code/error.key</v>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.detail.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>TASKS-FILTERS-001</v>
+      </c>
+      <c r="B104" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C104" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/analytics/saved-filters</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Task analytics saved filters</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Authorized user lists saved analytics filters</v>
+      </c>
+      <c r="G104" t="str">
+        <v>HTTP 2xx; JSON success envelope with data array</v>
+      </c>
+      <c r="H104" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I104" t="str">
+        <v>GET orgs/{orgId}/branches/{branchId}/tasks/analytics/saved-filters | expectSuccessStatus, expectJsonSuccessBody, Array.isArray(body.data)</v>
+      </c>
+      <c r="J104" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K104">
+        <v>2732</v>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.saved-filters.spec.js</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>TASKS-LIST-001</v>
+      </c>
+      <c r="B105" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C105" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D99" t="str">
+      <c r="D105" t="str">
+        <v>List tasks</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Authorized owner lists tasks with pagination and filters</v>
+      </c>
+      <c r="G105" t="str">
+        <v>HTTP 2xx, JSON</v>
+      </c>
+      <c r="H105" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I105" t="str">
+        <v>JWT via loginWithOtp (owner persona) | GET orgs/{orgId}/branches/{branchId}/tasks with page=1&amp;pageSize=20&amp;q=inventory&amp;sort=startAt&amp;order=asc | expectTasksListSuccessBody: | success=true, statusCode=200, string message | data is an array | pagination.type=offset | pagination.page&gt;=1, pagination.limit&gt;0 &amp;&amp; &lt;=100 | pagination.total&gt;=0, pagination.totalPages&gt;=1</v>
+      </c>
+      <c r="J105" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K105">
+        <v>2366</v>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.list.spec.js</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>TASKS-LIST-002</v>
+      </c>
+      <c r="B106" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C106" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D106" t="str">
+        <v>List tasks</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Unauthorized tasks list request returns 401</v>
+      </c>
+      <c r="G106" t="str">
+        <v>HTTP 401</v>
+      </c>
+      <c r="H106" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I106" t="str">
+        <v>expectHttpStatus 401 | JSON Content-Type | expectJsonErrorBody: | statusCode=401 | message contains Authentication | non-empty error.code and error.key</v>
+      </c>
+      <c r="J106" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K106">
+        <v>348</v>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>TASKS-LIST-003</v>
+      </c>
+      <c r="B107" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C107" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D107" t="str">
         <v>List tasks access by role</v>
       </c>
-      <c r="E99" t="str">
+      <c r="E107" t="str">
         <v>Regression</v>
       </c>
-      <c r="F99" t="str">
+      <c r="F107" t="str">
+        <v>Owner branch tasks list returns successfully</v>
+      </c>
+      <c r="G107" t="str">
+        <v>HTTP 2xx</v>
+      </c>
+      <c r="H107" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I107" t="str">
+        <v>expectTasksListSuccessBody with owner JWT and TASKS_BRANCH_ID</v>
+      </c>
+      <c r="J107" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K107">
+        <v>2380</v>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107" t="str">
+        <v>tests/api/regression/tasks.list.access.spec.js</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>TASKS-LIST-004</v>
+      </c>
+      <c r="B108" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C108" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D108" t="str">
+        <v>List tasks access by role</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="F108" t="str">
         <v>Supervisor branch tasks list returns successfully</v>
       </c>
-      <c r="G99" t="str">
+      <c r="G108" t="str">
         <v>HTTP 2xx</v>
       </c>
-      <c r="H99" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I99" t="str">
+      <c r="H108" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I108" t="str">
         <v>expectTasksListSuccessBody with supervisor JWT and branch from token (fallback env)</v>
       </c>
-      <c r="J99" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K99">
-        <v>2528</v>
-      </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
-      <c r="M99" t="str">
+      <c r="J108" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K108">
+        <v>2216</v>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
         <v>tests/api/regression/tasks.list.access.spec.js</v>
       </c>
     </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100" t="str">
+    <row r="109" xml:space="preserve">
+      <c r="A109" t="str">
         <v>TASKS-LIST-005</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B109" t="str">
         <v>GET</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C109" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D100" t="str">
+      <c r="D109" t="str">
         <v>List tasks access by role</v>
       </c>
-      <c r="E100" t="str">
+      <c r="E109" t="str">
         <v>Regression</v>
       </c>
-      <c r="F100" t="str">
+      <c r="F109" t="str">
         <v>Employee scoped tasks list returns successfully</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G109" t="str">
         <v>HTTP 2xx</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H109" t="str">
         <v>failed</v>
       </c>
-      <c r="I100" t="str">
+      <c r="I109" t="str">
         <v>expectTasksListSuccessBody with employee JWT and branch from token (fallback env)</v>
       </c>
-      <c r="J100" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K100">
-        <v>1984</v>
-      </c>
-      <c r="L100" t="str" xml:space="preserve">
+      <c r="J109" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K109">
+        <v>1934</v>
+      </c>
+      <c r="L109" t="str" xml:space="preserve">
         <v xml:space="preserve">Error: Expected 2xx, got HTTP 401 — Authentication required.
 _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
 Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
-      <c r="M100" t="str">
+      <c r="M109" t="str">
         <v>tests/api/regression/tasks.list.access.spec.js</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="str">
+    <row r="110">
+      <c r="A110" t="str">
         <v>TASKS-LIST-006</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B110" t="str">
         <v>GET</v>
       </c>
-      <c r="C101" t="str">
+      <c r="C110" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D101" t="str">
+      <c r="D110" t="str">
         <v>List tasks</v>
       </c>
-      <c r="E101" t="str">
+      <c r="E110" t="str">
         <v>Smoke</v>
       </c>
-      <c r="F101" t="str">
+      <c r="F110" t="str">
         <v>Board view task list returns successfully</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G110" t="str">
         <v>HTTP 2xx</v>
       </c>
-      <c r="H101" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I101" t="str">
+      <c r="H110" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I110" t="str">
         <v>Board endpoint returns success envelope with task rows</v>
       </c>
-      <c r="J101" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K101">
-        <v>1867</v>
-      </c>
-      <c r="L101" t="str">
-        <v/>
-      </c>
-      <c r="M101" t="str">
+      <c r="J110" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K110">
+        <v>2832</v>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
         <v>tests/api/modules/tasks/smoke/tasks.boardview.spec.js</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="str">
+    <row r="111">
+      <c r="A111" t="str">
         <v>TASKS-LIST-007</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B111" t="str">
         <v>GET</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C111" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D102" t="str">
+      <c r="D111" t="str">
         <v>List tasks</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E111" t="str">
         <v>Smoke</v>
       </c>
-      <c r="F102" t="str">
+      <c r="F111" t="str">
         <v>Filtered board view with assigneeId returns successfully</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G111" t="str">
         <v>HTTP 2xx</v>
       </c>
-      <c r="H102" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I102" t="str">
+      <c r="H111" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I111" t="str">
         <v>Board endpoint returns filtered rows for assignee query</v>
       </c>
-      <c r="J102" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K102">
-        <v>2081</v>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102" t="str">
+      <c r="J111" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K111">
+        <v>1432</v>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
         <v>tests/api/modules/tasks/smoke/tasks.boardview.spec.js</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="str">
+    <row r="112">
+      <c r="A112" t="str">
         <v>TASKS-LIST-008</v>
       </c>
-      <c r="B103" t="str">
+      <c r="B112" t="str">
         <v>GET</v>
       </c>
-      <c r="C103" t="str">
+      <c r="C112" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D103" t="str">
+      <c r="D112" t="str">
         <v>List tasks</v>
       </c>
-      <c r="E103" t="str">
+      <c r="E112" t="str">
         <v>Smoke</v>
       </c>
-      <c r="F103" t="str">
+      <c r="F112" t="str">
         <v>Task detail endpoint returns selected task payload</v>
       </c>
-      <c r="G103" t="str">
+      <c r="G112" t="str">
         <v>HTTP 2xx</v>
       </c>
-      <c r="H103" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I103" t="str">
+      <c r="H112" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I112" t="str">
         <v>Task detail endpoint returns success envelope with selected task</v>
       </c>
-      <c r="J103" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K103">
-        <v>2820</v>
-      </c>
-      <c r="L103" t="str">
-        <v/>
-      </c>
-      <c r="M103" t="str">
+      <c r="J112" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K112">
+        <v>1517</v>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
         <v>tests/api/modules/tasks/smoke/tasks.boardview.spec.js</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="str">
+    <row r="113">
+      <c r="A113" t="str">
         <v>TASKS-LIST-009</v>
       </c>
-      <c r="B104" t="str">
+      <c r="B113" t="str">
         <v>GET</v>
       </c>
-      <c r="C104" t="str">
+      <c r="C113" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D104" t="str">
+      <c r="D113" t="str">
         <v>List tasks access by role</v>
       </c>
-      <c r="E104" t="str">
+      <c r="E113" t="str">
         <v>Regression</v>
       </c>
-      <c r="F104" t="str">
+      <c r="F113" t="str">
         <v>Forbidden supervisor cross-branch task list request is rejected</v>
       </c>
-      <c r="G104" t="str">
+      <c r="G113" t="str">
         <v>HTTP 4xx</v>
       </c>
-      <c r="H104" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I104" t="str">
+      <c r="H113" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I113" t="str">
         <v>Supervisor token requests another branch tasks; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
-      <c r="J104" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K104">
-        <v>6951</v>
-      </c>
-      <c r="L104" t="str">
-        <v/>
-      </c>
-      <c r="M104" t="str">
+      <c r="J113" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K113">
+        <v>7260</v>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
         <v>tests/api/regression/tasks.list.access.spec.js</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="str">
+    <row r="114">
+      <c r="A114" t="str">
         <v>TASKS-LIST-010</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B114" t="str">
         <v>GET</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C114" t="str">
         <v>/orgs/:orgId/branches/:branchId/tasks</v>
       </c>
-      <c r="D105" t="str">
+      <c r="D114" t="str">
         <v>List tasks access by role</v>
       </c>
-      <c r="E105" t="str">
+      <c r="E114" t="str">
         <v>Regression</v>
       </c>
-      <c r="F105" t="str">
+      <c r="F114" t="str">
         <v>Forbidden employee cross-branch task list request is rejected</v>
       </c>
-      <c r="G105" t="str">
+      <c r="G114" t="str">
         <v>HTTP 4xx</v>
       </c>
-      <c r="H105" t="str">
-        <v>passed</v>
-      </c>
-      <c r="I105" t="str">
+      <c r="H114" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I114" t="str">
         <v>Employee token requests another branch tasks; response must be JSON error envelope with non-empty error.code and error.key</v>
       </c>
-      <c r="J105" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
-      </c>
-      <c r="K105">
-        <v>5196</v>
-      </c>
-      <c r="L105" t="str">
-        <v/>
-      </c>
-      <c r="M105" t="str">
+      <c r="J114" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K114">
+        <v>5809</v>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114" t="str">
         <v>tests/api/regression/tasks.list.access.spec.js</v>
       </c>
     </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str">
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str">
+        <v>TASKS-LIST-011</v>
+      </c>
+      <c r="B115" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C115" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D115" t="str">
+        <v>List tasks</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F115" t="str">
+        <v>Tasks list rejects pageSize above API maximum (100)</v>
+      </c>
+      <c r="G115" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H115" t="str">
+        <v>failed</v>
+      </c>
+      <c r="I115" t="str">
+        <v>GET orgs/{orgId}/branches/{branchId}/tasks with pageSize=101 | expectHttpStatus 422 or 400 | expectJsonContentType | expectJsonErrorBody with success=false, non-empty error.code</v>
+      </c>
+      <c r="J115" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K115">
+        <v>2348</v>
+      </c>
+      <c r="L115" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m
+Expected: _x001b_[32m"string"_x001b_[39m
+Received: _x001b_[31m"undefined"_x001b_[39m</v>
+      </c>
+      <c r="M115" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>TASKS-LIST-012</v>
+      </c>
+      <c r="B116" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C116" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D116" t="str">
+        <v>List tasks</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F116" t="str">
+        <v>Authorized owner lists tasks with all supported query parameters in one request</v>
+      </c>
+      <c r="G116" t="str">
+        <v>HTTP 2xx; JSON success list envelope</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>Preload GET .../tasks/board to discover valid statusId, priorityId, assigneeId, and a task startAt | GET orgs/{orgId}/branches/{branchId}/tasks with q, statusId, priorityId, assigneeId, from, to, page, pageSize, sort, order | expectSuccessStatus, expectJsonContentType, expectTasksListSuccessBody</v>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.list.spec.js</v>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str">
+        <v>TASKS-NOTIF-001</v>
+      </c>
+      <c r="B117" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C117" t="str">
+        <v>/orgs/:orgId/branches/:branchId/task-notifications</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Task notifications</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F117" t="str">
+        <v>Authorized user lists branch task notifications</v>
+      </c>
+      <c r="G117" t="str">
+        <v>HTTP 2xx; JSON success envelope with data array</v>
+      </c>
+      <c r="H117" t="str">
+        <v>failed</v>
+      </c>
+      <c r="I117" t="str">
+        <v>GET orgs/{orgId}/branches/{branchId}/task-notifications?page=1&amp;limit=20 | expectSuccessStatus, expectJsonSuccessBody, Array.isArray(body.data)</v>
+      </c>
+      <c r="J117" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K117">
+        <v>1742</v>
+      </c>
+      <c r="L117" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 422 — Validation failed.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="M117" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.notifications.spec.js</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>TASKS-PATCH-001</v>
+      </c>
+      <c r="B118" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C118" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Tasks CRUD</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F118" t="str">
+        <v>Authorized user updates a task created in the same serial suite</v>
+      </c>
+      <c r="G118" t="str">
+        <v>HTTP 2xx; JSON success envelope with data.taskId</v>
+      </c>
+      <c r="H118" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I118" t="str">
+        <v>PATCH orgs/{orgId}/branches/{branchId}/tasks/{taskId} with partial body | expectSuccessStatus, expectJsonSuccessBody with messageIncludes updated</v>
+      </c>
+      <c r="J118" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K118">
+        <v>304</v>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>TASKS-PATCH-002</v>
+      </c>
+      <c r="B119" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C119" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Update task using all editable fields (title, description, statusId, priorityId, assigneeId, startAt, endAt, reminderOffsetsMinutes)</v>
+      </c>
+      <c r="G119" t="str">
+        <v>HTTP 2xx; JSON success envelope with data.taskId</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v>expectSuccessStatus, expectJsonSuccessBody message includes updated</v>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.update.spec.js</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>TASKS-PATCH-003</v>
+      </c>
+      <c r="B120" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C120" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F120" t="str">
+        <v>Reminder replacement flow when reminderOffsetsMinutes is provided</v>
+      </c>
+      <c r="G120" t="str">
+        <v>HTTP 2xx for patch and detail fetch; detail contains reminders array</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>Patch with new reminder offsets, then GET detail and validate data.reminders exists as array</v>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.update.spec.js</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>TASKS-PATCH-004</v>
+      </c>
+      <c r="B121" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C121" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F121" t="str">
+        <v>Invalid timeline update (endAt &lt;= startAt)</v>
+      </c>
+      <c r="G121" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>TASKS-PATCH-005</v>
+      </c>
+      <c r="B122" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C122" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D122" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F122" t="str">
+        <v>Subtask timeline update outside parent timeline is blocked</v>
+      </c>
+      <c r="G122" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v>Create parent + subtask seed, patch subtask outside parent range, assert error envelope</v>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>TASKS-PATCH-006</v>
+      </c>
+      <c r="B123" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C123" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F123" t="str">
+        <v>Parent timeline shrink blocked when subtasks would fall outside</v>
+      </c>
+      <c r="G123" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v>Create parent + subtask seed, shrink parent end time below child window, assert error envelope</v>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>TASKS-PATCH-007</v>
+      </c>
+      <c r="B124" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C124" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F124" t="str">
+        <v>Missing JWT on update request</v>
+      </c>
+      <c r="G124" t="str">
+        <v>HTTP 401; JSON authentication error envelope</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v>expectHttpStatus 401 + expectJsonErrorBody auth contract</v>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>TASKS-PATCH-008</v>
+      </c>
+      <c r="B125" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C125" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F125" t="str">
+        <v>Unknown task ID on update</v>
+      </c>
+      <c r="G125" t="str">
+        <v>HTTP 404; JSON error envelope</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v>expectHttpStatus 404 + expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TASKS-PATCH-009</v>
+      </c>
+      <c r="B126" t="str">
+        <v>PATCH</v>
+      </c>
+      <c r="C126" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Update task</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F126" t="str">
+        <v>Cross-branch update attempt is rejected</v>
+      </c>
+      <c r="G126" t="str">
+        <v>HTTP 403 or 404; JSON error envelope</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>Supervisor token patches task via unauthorized branch path and receives policy/scope rejection</v>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.update.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>TASKS-POST-001</v>
+      </c>
+      <c r="B127" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C127" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Tasks CRUD</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F127" t="str">
+        <v>Authorized user creates a task and receives taskId</v>
+      </c>
+      <c r="G127" t="str">
+        <v>HTTP 200 or 201; JSON success envelope with data.taskId</v>
+      </c>
+      <c r="H127" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I127" t="str">
+        <v>JWT via loginWithOtp | POST orgs/{orgId}/branches/{branchId}/tasks with ISO startAt/endAt and valid UUID references from list row | expectHttpOkOrCreated, expectJsonSuccessBody with messageIncludes created, data.taskId non-empty</v>
+      </c>
+      <c r="J127" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K127">
+        <v>690</v>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>TASKS-POST-002</v>
+      </c>
+      <c r="B128" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C128" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Tasks CRUD</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F128" t="str">
+        <v>Create recurring task returns taskId and recurrenceId</v>
+      </c>
+      <c r="G128" t="str">
+        <v>HTTP 200 or 201; JSON success envelope with non-empty data.taskId and data.recurrenceId</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v>POST orgs/{orgId}/branches/{branchId}/tasks with valid recurrence object (frequency, executionTime, endDate) | expectHttpOkOrCreated, expectJsonSuccessBody with non-empty data.taskId and data.recurrenceId | Cleanup delete for created recurrence task</v>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TASKS-POST-003</v>
+      </c>
+      <c r="B129" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C129" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F129" t="str">
+        <v>Missing required startAt in create payload</v>
+      </c>
+      <c r="G129" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>TASKS-POST-004</v>
+      </c>
+      <c r="B130" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C130" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F130" t="str">
+        <v>endAt not after startAt violates timeline rule</v>
+      </c>
+      <c r="G130" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TASKS-POST-005</v>
+      </c>
+      <c r="B131" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C131" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F131" t="str">
+        <v>Invalid UUID values for statusId, priorityId, and assigneeId</v>
+      </c>
+      <c r="G131" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TASKS-POST-006</v>
+      </c>
+      <c r="B132" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C132" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E132" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F132" t="str">
+        <v>Invalid reminder offsets (negative/non-numeric)</v>
+      </c>
+      <c r="G132" t="str">
+        <v>HTTP 422 or 400; JSON error envelope</v>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TASKS-POST-007</v>
+      </c>
+      <c r="B133" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C133" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F133" t="str">
+        <v>Missing JWT while creating task</v>
+      </c>
+      <c r="G133" t="str">
+        <v>HTTP 401; JSON error envelope</v>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v>expectHttpStatus 401 + authentication error contract</v>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>TASKS-POST-008</v>
+      </c>
+      <c r="B134" t="str">
+        <v>POST</v>
+      </c>
+      <c r="C134" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Create task</v>
+      </c>
+      <c r="E134" t="str">
+        <v>Negative</v>
+      </c>
+      <c r="F134" t="str">
+        <v>Cross-branch unauthorized create attempt with supervisor token</v>
+      </c>
+      <c r="G134" t="str">
+        <v>HTTP 403 or 404; JSON error envelope</v>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v>expectJsonErrorBody with non-empty error.code and error.key</v>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
+        <v>tests/api/modules/tasks/negative/tasks.create.negative.spec.js</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>TASKS-SETTINGS-001</v>
+      </c>
+      <c r="B135" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C135" t="str">
+        <v>/orgs/:orgId/task-settings/statuses</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Task settings</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F135" t="str">
+        <v>Owner lists org task statuses</v>
+      </c>
+      <c r="G135" t="str">
+        <v>HTTP 2xx; JSON success envelope with data array of statuses</v>
+      </c>
+      <c r="H135" t="str">
+        <v>passed</v>
+      </c>
+      <c r="I135" t="str">
+        <v>JWT owner persona | GET orgs/{orgId}/task-settings/statuses | expectSuccessStatus, expectJsonSuccessBody, Array.isArray(body.data); first row has id and name strings when non-empty</v>
+      </c>
+      <c r="J135" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K135">
+        <v>1566</v>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.settings.spec.js</v>
+      </c>
+    </row>
+    <row r="136" xml:space="preserve">
+      <c r="A136" t="str">
+        <v>TASKS-SUBTREE-001</v>
+      </c>
+      <c r="B136" t="str">
+        <v>GET</v>
+      </c>
+      <c r="C136" t="str">
+        <v>/orgs/:orgId/branches/:branchId/tasks/:taskId/subtasks/tree</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Task subtasks tree</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Smoke</v>
+      </c>
+      <c r="F136" t="str">
+        <v>Authorized user loads subtask tree for a board task</v>
+      </c>
+      <c r="G136" t="str">
+        <v>HTTP 2xx; response is JSON array (envelope data or raw array)</v>
+      </c>
+      <c r="H136" t="str">
+        <v>failed</v>
+      </c>
+      <c r="I136" t="str">
+        <v>GET .../tasks/{taskId}/subtasks/tree | expectSuccessStatus, expectJsonContentType | Parsed tree is Array.isArray from body or body.data</v>
+      </c>
+      <c r="J136" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="K136">
+        <v>3468</v>
+      </c>
+      <c r="L136" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+      <c r="M136" t="str">
+        <v>tests/api/modules/tasks/smoke/tasks.subtasks-tree.spec.js</v>
+      </c>
+    </row>
+    <row r="137" xml:space="preserve">
+      <c r="A137" t="str">
         <v>TEMPLATE-001</v>
       </c>
-      <c r="B106" t="str">
+      <c r="B137" t="str">
         <v>TEMPLATE</v>
       </c>
-      <c r="C106" t="str">
+      <c r="C137" t="str">
         <v>endpoint</v>
       </c>
-      <c r="D106" t="str">
+      <c r="D137" t="str">
         <v>Template API</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E137" t="str">
         <v>Smoke</v>
       </c>
-      <c r="F106" t="str">
+      <c r="F137" t="str">
         <v>Successful METHOD /your/endpoint returns expected behavior</v>
       </c>
-      <c r="G106" t="str">
+      <c r="G137" t="str">
         <v>Replace with endpoint-specific expected status/body</v>
       </c>
-      <c r="H106" t="str">
+      <c r="H137" t="str">
         <v>failed</v>
       </c>
-      <c r="I106" t="str">
+      <c r="I137" t="str">
         <v>Template placeholder scenario for new module onboarding</v>
       </c>
-      <c r="J106" t="str">
+      <c r="J137" t="str">
         <v>2026-04-29T06:23:24.714Z</v>
       </c>
-      <c r="K106">
+      <c r="K137">
         <v>2213</v>
       </c>
-      <c r="L106" t="str" xml:space="preserve">
+      <c r="L137" t="str" xml:space="preserve">
         <v xml:space="preserve">Error: Expected 2xx, got HTTP 404 — Cannot POST /api/v1/orgs/ccbebccf-fdfe-4d4c-8256-5149ccfb683f/branches/5b472583-4f39-4460-a56b-a7aa1860ddbd/your-endpoint
 _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
 Received: _x001b_[31mfalse_x001b_[39m</v>
       </c>
-      <c r="M106" t="str">
+      <c r="M137" t="str">
         <v>tests/api/modules/template/smoke/api.template.spec.js</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M137"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H1050"/>
+  <dimension ref="A1:H1257"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -32121,9 +33399,5406 @@
         <v/>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1051" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>AUTH-FORGOT-003</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>api/modules/auth/negative/auth.forgot-password.negative.spec.js</v>
+      </c>
+      <c r="E1051" t="str">
+        <v>[AUTH-FORGOT-003] : Missing email returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1051" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1051">
+        <v>928</v>
+      </c>
+      <c r="H1051" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1052" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>AUTH-LOGIN-002</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1052" t="str">
+        <v>[AUTH-LOGIN-002] : Invalid password returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1052" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1052">
+        <v>1039</v>
+      </c>
+      <c r="H1052" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1053" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>AUTH-LOGIN-003</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1053" t="str">
+        <v>[AUTH-LOGIN-003] : Unknown email returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1053" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1053">
+        <v>248</v>
+      </c>
+      <c r="H1053" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1054" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>AUTH-LOGIN-004</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1054" t="str">
+        <v>[AUTH-LOGIN-004] : Missing email returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1054" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1054">
+        <v>495</v>
+      </c>
+      <c r="H1054" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1055" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>AUTH-LOGIN-005</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1055" t="str">
+        <v>[AUTH-LOGIN-005] : Missing password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1055" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1055">
+        <v>289</v>
+      </c>
+      <c r="H1055" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1056" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>AUTH-LOGIN-006</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1056" t="str">
+        <v>[AUTH-LOGIN-006] : Invalid email format returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1056" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1056">
+        <v>237</v>
+      </c>
+      <c r="H1056" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1057" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>AUTH-LOGIN-007</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1057" t="str">
+        <v>[AUTH-LOGIN-007] : Empty password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1057" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1057">
+        <v>233</v>
+      </c>
+      <c r="H1057" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1058" xml:space="preserve">
+      <c r="A1058" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1058" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>AUTH-LOGIN-008</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1058" t="str">
+        <v>[AUTH-LOGIN-008] : Trimmed email with extra spaces is accepted → 200</v>
+      </c>
+      <c r="F1058" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1058">
+        <v>231</v>
+      </c>
+      <c r="H1058" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 422 — Validation failed.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1059" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>AUTH-LOGIN-009</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1059" t="str">
+        <v>[AUTH-LOGIN-009] : Uppercase email is accepted → 200</v>
+      </c>
+      <c r="F1059" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1059">
+        <v>1163</v>
+      </c>
+      <c r="H1059" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1060" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>AUTH-PACT-001</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>api/modules/auth/negative/auth.password-action.negative.spec.js</v>
+      </c>
+      <c r="E1060" t="str">
+        <v>[AUTH-PACT-001] : Missing token returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1060" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1060">
+        <v>946</v>
+      </c>
+      <c r="H1060" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1061" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>AUTH-PACT-002</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>api/modules/auth/negative/auth.password-action.negative.spec.js</v>
+      </c>
+      <c r="E1061" t="str">
+        <v>[AUTH-PACT-002] : Invalid or unknown token returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1061" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1061">
+        <v>280</v>
+      </c>
+      <c r="H1061" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1062" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>AUTH-REFRESH-002</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1062" t="str">
+        <v>[AUTH-REFRESH-002] : Missing refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1062" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1062">
+        <v>877</v>
+      </c>
+      <c r="H1062" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1063" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>AUTH-REFRESH-003</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1063" t="str">
+        <v>[AUTH-REFRESH-003] : Malformed refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1063" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1063">
+        <v>286</v>
+      </c>
+      <c r="H1063" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1064" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>AUTH-REFRESH-004</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1064" t="str">
+        <v>[AUTH-REFRESH-004] : Unknown refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1064" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1064">
+        <v>265</v>
+      </c>
+      <c r="H1064" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1065" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>AUTH-REFRESH-005</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1065" t="str">
+        <v>[AUTH-REFRESH-005] : Reused refresh token after rotation returns 401 Unauthorized → 200</v>
+      </c>
+      <c r="F1065" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1065">
+        <v>2891</v>
+      </c>
+      <c r="H1065" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1066" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>AUTH-SENDOTP-002</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1066" t="str">
+        <v>[AUTH-SENDOTP-002] : Missing loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1066" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1066">
+        <v>921</v>
+      </c>
+      <c r="H1066" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1067" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>AUTH-SENDOTP-003</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1067" t="str">
+        <v>[AUTH-SENDOTP-003] : Empty loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1067" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1067">
+        <v>282</v>
+      </c>
+      <c r="H1067" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1068" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>AUTH-SENDOTP-004</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1068" t="str">
+        <v>[AUTH-SENDOTP-004] : Unsupported SMS method returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1068" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1068">
+        <v>1167</v>
+      </c>
+      <c r="H1068" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1069" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>AUTH-SENDOTP-005</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1069" t="str">
+        <v>[AUTH-SENDOTP-005] : Invalid loginAttemptId returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1069" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1069">
+        <v>263</v>
+      </c>
+      <c r="H1069" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1070" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>AUTH-SETPW-001</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>api/modules/auth/negative/auth.set-password.negative.spec.js</v>
+      </c>
+      <c r="E1070" t="str">
+        <v>[AUTH-SETPW-001] : Weak password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1070" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1070">
+        <v>823</v>
+      </c>
+      <c r="H1070" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1071" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>AUTH-SETPW-002</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>api/modules/auth/negative/auth.set-password.negative.spec.js</v>
+      </c>
+      <c r="E1071" t="str">
+        <v>[AUTH-SETPW-002] : Mismatched passwords return 400 Bad Request → 400</v>
+      </c>
+      <c r="F1071" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1071">
+        <v>252</v>
+      </c>
+      <c r="H1071" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1072" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>AUTH-VERIFY-002</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1072" t="str">
+        <v>[AUTH-VERIFY-002] : Missing OTP generation returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1072" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1072">
+        <v>872</v>
+      </c>
+      <c r="H1072" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1073" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>AUTH-VERIFY-003</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1073" t="str">
+        <v>[AUTH-VERIFY-003] : Invalid OTP returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1073" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1073">
+        <v>1154</v>
+      </c>
+      <c r="H1073" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1074" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>AUTH-VERIFY-004</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1074" t="str">
+        <v>[AUTH-VERIFY-004] : Missing loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1074" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1074">
+        <v>290</v>
+      </c>
+      <c r="H1074" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1075" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>AUTH-VERIFY-005</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1075" t="str">
+        <v>[AUTH-VERIFY-005] : Missing otp returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1075" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1075">
+        <v>1032</v>
+      </c>
+      <c r="H1075" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1076" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>AUTH-VERIFY-006</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1076" t="str">
+        <v>[AUTH-VERIFY-006] : Reused OTP attempt returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1076" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1076">
+        <v>1651</v>
+      </c>
+      <c r="H1076" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1077" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>AUTH-LOGIN-001</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>api/modules/auth/smoke/auth.login.spec.js</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>[AUTH-LOGIN-001] : Valid credentials → OTP challenge → 200</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1077">
+        <v>597</v>
+      </c>
+      <c r="H1077" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1078" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>AUTH-REFRESH-001</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>api/modules/auth/smoke/auth.refresh.spec.js</v>
+      </c>
+      <c r="E1078" t="str">
+        <v>[AUTH-REFRESH-001] : Successful OTP flow refreshes token with JSON refreshToken → 200</v>
+      </c>
+      <c r="F1078" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1078">
+        <v>2631</v>
+      </c>
+      <c r="H1078" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1079" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>AUTH-SENDOTP-001</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>api/modules/auth/smoke/auth.send-otp.spec.js</v>
+      </c>
+      <c r="E1079" t="str">
+        <v>[AUTH-SENDOTP-001] : Successful login sends OTP with EMAIL method → 200</v>
+      </c>
+      <c r="F1079" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1079">
+        <v>893</v>
+      </c>
+      <c r="H1079" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1080" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>AUTH-VERIFY-001</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>api/modules/auth/smoke/auth.verify-otp.spec.js</v>
+      </c>
+      <c r="E1080" t="str">
+        <v>[AUTH-VERIFY-001] : Successful login-send-otp-verify flow returns tokens → 200</v>
+      </c>
+      <c r="F1080" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1080">
+        <v>1553</v>
+      </c>
+      <c r="H1080" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1081" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>TASKS-LIST-002</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+      </c>
+      <c r="E1081" t="str">
+        <v>[TASKS-LIST-002] : Unauthorized tasks list request returns 401 → 401</v>
+      </c>
+      <c r="F1081" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1081">
+        <v>256</v>
+      </c>
+      <c r="H1081" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1082" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>TASKS-LIST-006</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1082" t="str">
+        <v>[TASKS-LIST-006] : Board view task list returns successfully → 2XX</v>
+      </c>
+      <c r="F1082" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1082">
+        <v>1867</v>
+      </c>
+      <c r="H1082" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1083" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>TASKS-LIST-007</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1083" t="str">
+        <v>[TASKS-LIST-007] : Filtered board view with assigneeId returns successfully → 2XX</v>
+      </c>
+      <c r="F1083" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1083">
+        <v>2081</v>
+      </c>
+      <c r="H1083" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1084" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>TASKS-LIST-008</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1084" t="str">
+        <v>[TASKS-LIST-008] : Task detail endpoint returns selected task payload → 2XX</v>
+      </c>
+      <c r="F1084" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1084">
+        <v>2820</v>
+      </c>
+      <c r="H1084" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1085" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>TASKS-LIST-001</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>api/modules/tasks/smoke/tasks.list.spec.js</v>
+      </c>
+      <c r="E1085" t="str">
+        <v>[TASKS-LIST-001] : Authorized owner lists tasks with pagination and filters → 2XX</v>
+      </c>
+      <c r="F1085" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1085">
+        <v>2031</v>
+      </c>
+      <c r="H1085" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1086" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>ORGS-CREATE-002</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>api/modules/users/negative/users.create.negative.spec.js</v>
+      </c>
+      <c r="E1086" t="str">
+        <v>[ORGS-CREATE-002] : Unauthorized create request returns 401 → 401</v>
+      </c>
+      <c r="F1086" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1086">
+        <v>263</v>
+      </c>
+      <c r="H1086" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1087" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>ORGS-CREATE-003</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>api/modules/users/negative/users.create.negative.spec.js</v>
+      </c>
+      <c r="E1087" t="str">
+        <v>[ORGS-CREATE-003] : Missing email on create returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1087" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1087">
+        <v>2203</v>
+      </c>
+      <c r="H1087" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1088" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>ORGS-USERS-GET-002</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>api/modules/users/negative/users.get.negative.spec.js</v>
+      </c>
+      <c r="E1088" t="str">
+        <v>[ORGS-USERS-GET-002] : Unauthorized request without Authorization header → 401</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1088">
+        <v>282</v>
+      </c>
+      <c r="H1088" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1089" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>ORGS-USERS-002</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>api/modules/users/negative/users.list.negative.spec.js</v>
+      </c>
+      <c r="E1089" t="str">
+        <v>[ORGS-USERS-002] : Unauthorized request without Authorization header → 401</v>
+      </c>
+      <c r="F1089" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1089">
+        <v>267</v>
+      </c>
+      <c r="H1089" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1090" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>ORGS-OPTS-002</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>api/modules/users/negative/users.options.negative.spec.js</v>
+      </c>
+      <c r="E1090" t="str">
+        <v>[ORGS-OPTS-002] : Unauthorized request without Authorization → 401</v>
+      </c>
+      <c r="F1090" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1090">
+        <v>269</v>
+      </c>
+      <c r="H1090" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1091" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>ORGS-CREATE-001</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>api/modules/users/smoke/users.create.spec.js</v>
+      </c>
+      <c r="E1091" t="str">
+        <v>[ORGS-CREATE-001] : Authorized owner creates user with minimal body → 2XX</v>
+      </c>
+      <c r="F1091" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1091">
+        <v>2224</v>
+      </c>
+      <c r="H1091" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1092" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>ORGS-USERS-GET-001</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>api/modules/users/smoke/users.get.spec.js</v>
+      </c>
+      <c r="E1092" t="str">
+        <v>[ORGS-USERS-GET-001] : Authorized owner gets caller orgUserId details → 200</v>
+      </c>
+      <c r="F1092" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1092">
+        <v>2475</v>
+      </c>
+      <c r="H1092" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1093" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>ORGS-USERS-001</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>api/modules/users/smoke/users.list.spec.js</v>
+      </c>
+      <c r="E1093" t="str">
+        <v>[ORGS-USERS-001] : Authorized owner lists users with page and limit → 200</v>
+      </c>
+      <c r="F1093" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1093">
+        <v>2313</v>
+      </c>
+      <c r="H1093" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1094" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>ORGS-OPTS-001</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>api/modules/users/smoke/users.options.spec.js</v>
+      </c>
+      <c r="E1094" t="str">
+        <v>[ORGS-OPTS-001] : Authorized supervisor gets options for session branchId → 200</v>
+      </c>
+      <c r="F1094" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1094">
+        <v>5201</v>
+      </c>
+      <c r="H1094" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1095" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1095" t="str">
+        <v>ORGS-PATCH-001</v>
+      </c>
+      <c r="D1095" t="str">
+        <v>api/modules/users/smoke/users.update.flow.spec.js</v>
+      </c>
+      <c r="E1095" t="str">
+        <v>[ORGS-PATCH-001] : Complete owner create-get-patch-get flow validates updates → 2XX</v>
+      </c>
+      <c r="F1095" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1095">
+        <v>3812</v>
+      </c>
+      <c r="H1095" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1096" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1096" t="str">
+        <v>AUTH-LOGIN-010</v>
+      </c>
+      <c r="D1096" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1096" t="str">
+        <v>[AUTH-LOGIN-010] : Valid seeded login succeeds → 200</v>
+      </c>
+      <c r="F1096" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1096">
+        <v>565</v>
+      </c>
+      <c r="H1096" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1097" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1097" t="str">
+        <v>AUTH-LOGIN-011</v>
+      </c>
+      <c r="D1097" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1097" t="str">
+        <v>[AUTH-LOGIN-011] : Uppercase email login succeeds → 200</v>
+      </c>
+      <c r="F1097" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1097">
+        <v>808</v>
+      </c>
+      <c r="H1097" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1098" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1098" t="str">
+        <v>AUTH-LOGIN-012</v>
+      </c>
+      <c r="D1098" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1098" t="str">
+        <v>[AUTH-LOGIN-012] : Wrong password returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1098" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1098">
+        <v>831</v>
+      </c>
+      <c r="H1098" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1099" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1099" t="str">
+        <v>AUTH-LOGIN-013</v>
+      </c>
+      <c r="D1099" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1099" t="str">
+        <v>[AUTH-LOGIN-013] : Unknown email returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1099" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1099">
+        <v>328</v>
+      </c>
+      <c r="H1099" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1100" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1100" t="str">
+        <v>AUTH-SENDOTP-006</v>
+      </c>
+      <c r="D1100" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1100" t="str">
+        <v>[AUTH-SENDOTP-006] : Valid loginAttemptId with EMAIL succeeds → 200</v>
+      </c>
+      <c r="F1100" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1100">
+        <v>677</v>
+      </c>
+      <c r="H1100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1101" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1101" t="str">
+        <v>AUTH-SENDOTP-007</v>
+      </c>
+      <c r="D1101" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1101" t="str">
+        <v>[AUTH-SENDOTP-007] : Unsupported SMS method returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1101" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1101">
+        <v>1204</v>
+      </c>
+      <c r="H1101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1102" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1102" t="str">
+        <v>AUTH-VERIFY-007</v>
+      </c>
+      <c r="D1102" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1102" t="str">
+        <v>[AUTH-VERIFY-007] : Valid static OTP after send-otp succeeds → 200</v>
+      </c>
+      <c r="F1102" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1102">
+        <v>1969</v>
+      </c>
+      <c r="H1102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1103" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1103" t="str">
+        <v>AUTH-VERIFY-008</v>
+      </c>
+      <c r="D1103" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1103" t="str">
+        <v>[AUTH-VERIFY-008] : Premature verify before send-otp returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1103" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1103">
+        <v>1152</v>
+      </c>
+      <c r="H1103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1104" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1104" t="str">
+        <v>AUTH-VERIFY-009</v>
+      </c>
+      <c r="D1104" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1104" t="str">
+        <v>[AUTH-VERIFY-009] : Wrong OTP returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1104" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1104">
+        <v>1237</v>
+      </c>
+      <c r="H1104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1105" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1105" t="str">
+        <v>AUTH-VERIFY-010</v>
+      </c>
+      <c r="D1105" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1105" t="str">
+        <v>[AUTH-VERIFY-010] : Double verify on same loginAttemptId returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1105" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1105">
+        <v>1808</v>
+      </c>
+      <c r="H1105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1106" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1106" t="str">
+        <v>AUTH-REFRESH-006</v>
+      </c>
+      <c r="D1106" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1106" t="str">
+        <v>[AUTH-REFRESH-006] : Valid body refreshToken refresh succeeds → 200</v>
+      </c>
+      <c r="F1106" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1106">
+        <v>2670</v>
+      </c>
+      <c r="H1106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1107" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1107" t="str">
+        <v>AUTH-REFRESH-007</v>
+      </c>
+      <c r="D1107" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1107" t="str">
+        <v>[AUTH-REFRESH-007] : Valid cookie-only refresh_token succeeds → 200</v>
+      </c>
+      <c r="F1107" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1107">
+        <v>2502</v>
+      </c>
+      <c r="H1107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1108" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1108" t="str">
+        <v>AUTH-REFRESH-008</v>
+      </c>
+      <c r="D1108" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1108" t="str">
+        <v>[AUTH-REFRESH-008] : Malformed refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1108" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1108">
+        <v>265</v>
+      </c>
+      <c r="H1108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1109" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1109" t="str">
+        <v>MISC-PROT-001</v>
+      </c>
+      <c r="D1109" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1109" t="str">
+        <v>[MISC-PROT-001] : Invalid JWT on protected GET returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1109" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1109">
+        <v>267</v>
+      </c>
+      <c r="H1109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1110" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1110" t="str">
+        <v>AUTH-VERIFY-011</v>
+      </c>
+      <c r="D1110" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1110" t="str">
+        <v>[AUTH-VERIFY-011] : Valid tier-3 member verify includes branch data → 200</v>
+      </c>
+      <c r="F1110" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1110">
+        <v>1684</v>
+      </c>
+      <c r="H1110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1111" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1111" t="str">
+        <v>TASKS-LIST-003</v>
+      </c>
+      <c r="D1111" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1111" t="str">
+        <v>[TASKS-LIST-003] : Owner branch tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1111" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1111">
+        <v>2785</v>
+      </c>
+      <c r="H1111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1112" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1112" t="str">
+        <v>TASKS-LIST-004</v>
+      </c>
+      <c r="D1112" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1112" t="str">
+        <v>[TASKS-LIST-004] : Supervisor branch tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1112" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1112">
+        <v>2528</v>
+      </c>
+      <c r="H1112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1113" xml:space="preserve">
+      <c r="A1113" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1113" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1113" t="str">
+        <v>TASKS-LIST-005</v>
+      </c>
+      <c r="D1113" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1113" t="str">
+        <v>[TASKS-LIST-005] : Employee scoped tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1113" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1113">
+        <v>1984</v>
+      </c>
+      <c r="H1113" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 401 — Authentication required.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1114" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1114" t="str">
+        <v>TASKS-LIST-009</v>
+      </c>
+      <c r="D1114" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1114" t="str">
+        <v>[TASKS-LIST-009] : Forbidden supervisor cross-branch task list request is rejected → 4XX</v>
+      </c>
+      <c r="F1114" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1114">
+        <v>6951</v>
+      </c>
+      <c r="H1114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1115" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1115" t="str">
+        <v>TASKS-LIST-010</v>
+      </c>
+      <c r="D1115" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1115" t="str">
+        <v>[TASKS-LIST-010] : Forbidden employee cross-branch task list request is rejected → 4XX</v>
+      </c>
+      <c r="F1115" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1115">
+        <v>5196</v>
+      </c>
+      <c r="H1115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1116" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1116" t="str">
+        <v>ORGS-PATCH-004</v>
+      </c>
+      <c r="D1116" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1116" t="str">
+        <v>[ORGS-PATCH-004] : Authorized owner updates user in own branch → 200</v>
+      </c>
+      <c r="F1116" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1116">
+        <v>2312</v>
+      </c>
+      <c r="H1116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1117" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1117" t="str">
+        <v>ORGS-PATCH-005</v>
+      </c>
+      <c r="D1117" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1117" t="str">
+        <v>[ORGS-PATCH-005] : Authorized supervisor updates user in own branch → 200</v>
+      </c>
+      <c r="F1117" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1117">
+        <v>2347</v>
+      </c>
+      <c r="H1117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1118" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>ORGS-CREATE-004</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1118" t="str">
+        <v>[ORGS-CREATE-004] : Forbidden employee create attempt is blocked → 401</v>
+      </c>
+      <c r="F1118" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1118">
+        <v>2488</v>
+      </c>
+      <c r="H1118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1119" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1119" t="str">
+        <v>ORGS-CREATE-016</v>
+      </c>
+      <c r="D1119" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1119" t="str">
+        <v>[ORGS-CREATE-016] : Missing required create fields return 422 Validation Error → 422</v>
+      </c>
+      <c r="F1119" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1119">
+        <v>1795</v>
+      </c>
+      <c r="H1119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1120" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1120" t="str">
+        <v>ORGS-CREATE-006</v>
+      </c>
+      <c r="D1120" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1120" t="str">
+        <v>[ORGS-CREATE-006] : Invalid supervisor branch override is rejected → 400</v>
+      </c>
+      <c r="F1120" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1120">
+        <v>1982</v>
+      </c>
+      <c r="H1120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1121" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1121" t="str">
+        <v>ORGS-PATCH-010</v>
+      </c>
+      <c r="D1121" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1121" t="str">
+        <v>[ORGS-PATCH-010] : Forbidden supervisor branchRole change is rejected → 400</v>
+      </c>
+      <c r="F1121" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1121">
+        <v>1855</v>
+      </c>
+      <c r="H1121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1122" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1122" t="str">
+        <v>ORGS-CREATE-008</v>
+      </c>
+      <c r="D1122" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1122" t="str">
+        <v>[ORGS-CREATE-008] : Duplicate membership in same org/branch is rejected → 400</v>
+      </c>
+      <c r="F1122" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1122">
+        <v>2068</v>
+      </c>
+      <c r="H1122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1123" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1123" t="str">
+        <v>ORGS-CREATE-009</v>
+      </c>
+      <c r="D1123" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1123" t="str">
+        <v>[ORGS-CREATE-009] : Invalid department id is rejected → 400</v>
+      </c>
+      <c r="F1123" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1123">
+        <v>1393</v>
+      </c>
+      <c r="H1123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1124" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1124" t="str">
+        <v>ORGS-CREATE-010</v>
+      </c>
+      <c r="D1124" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1124" t="str">
+        <v>[ORGS-CREATE-010] : Invalid supervisorOrgUserId is rejected → 400</v>
+      </c>
+      <c r="F1124" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1124">
+        <v>1565</v>
+      </c>
+      <c r="H1124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1125" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>ORGS-CREATE-011</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1125" t="str">
+        <v>[ORGS-CREATE-011] : Forbidden supervisor payroll fields are rejected → 400</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1125">
+        <v>1776</v>
+      </c>
+      <c r="H1125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1126" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>ORGS-CREATE-005</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1126" t="str">
+        <v>[ORGS-CREATE-005] : Valid supervisor creates employee in own branch → 2XX</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1126">
+        <v>1726</v>
+      </c>
+      <c r="H1126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1127" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1127" t="str">
+        <v>ORGS-PATCH-006</v>
+      </c>
+      <c r="D1127" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1127" t="str">
+        <v>[ORGS-PATCH-006] : Forbidden supervisor NI update is rejected → 400</v>
+      </c>
+      <c r="F1127" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1127">
+        <v>1703</v>
+      </c>
+      <c r="H1127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1128" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1128" t="str">
+        <v>ORGS-PATCH-007</v>
+      </c>
+      <c r="D1128" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1128" t="str">
+        <v>[ORGS-PATCH-007] : Forbidden supervisor share code update is rejected → 400</v>
+      </c>
+      <c r="F1128" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1128">
+        <v>1613</v>
+      </c>
+      <c r="H1128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1129" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1129" t="str">
+        <v>ORGS-PATCH-009</v>
+      </c>
+      <c r="D1129" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1129" t="str">
+        <v>[ORGS-PATCH-009] : Forbidden supervisor tax ID update is rejected → 400</v>
+      </c>
+      <c r="F1129" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1129">
+        <v>1581</v>
+      </c>
+      <c r="H1129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1130" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1130" t="str">
+        <v>ORGS-CREATE-007</v>
+      </c>
+      <c r="D1130" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1130" t="str">
+        <v>[ORGS-CREATE-007] : Forbidden supervisor-created SUPERVISOR role is rejected → 400</v>
+      </c>
+      <c r="F1130" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1130">
+        <v>1602</v>
+      </c>
+      <c r="H1130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1131" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1131" t="str">
+        <v>ORGS-PATCH-008</v>
+      </c>
+      <c r="D1131" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1131" t="str">
+        <v>[ORGS-PATCH-008] : Forbidden supervisor module permission update is rejected → 400</v>
+      </c>
+      <c r="F1131" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1131">
+        <v>1653</v>
+      </c>
+      <c r="H1131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1132" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1132" t="str">
+        <v>ORGS-USERS-GET-003</v>
+      </c>
+      <c r="D1132" t="str">
+        <v>api/regression/users.get.access.spec.js</v>
+      </c>
+      <c r="E1132" t="str">
+        <v>[ORGS-USERS-GET-003] : Forbidden employee access to another user detail is rejected → 4XX</v>
+      </c>
+      <c r="F1132" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1132">
+        <v>4105</v>
+      </c>
+      <c r="H1132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1133" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1133" t="str">
+        <v>ORGS-USERS-GET-004</v>
+      </c>
+      <c r="D1133" t="str">
+        <v>api/regression/users.get.access.spec.js</v>
+      </c>
+      <c r="E1133" t="str">
+        <v>[ORGS-USERS-GET-004] : Forbidden supervisor access to out-of-scope user detail is rejected → 4XX</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1133">
+        <v>3248</v>
+      </c>
+      <c r="H1133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1134" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1134" t="str">
+        <v>ORGS-PATCH-003</v>
+      </c>
+      <c r="D1134" t="str">
+        <v>api/regression/users.inactive-access.spec.js</v>
+      </c>
+      <c r="E1134" t="str">
+        <v>[ORGS-PATCH-003] : Inactive employee status blocks new session login → 200</v>
+      </c>
+      <c r="F1134" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1134">
+        <v>5373</v>
+      </c>
+      <c r="H1134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1135" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1135" t="str">
+        <v>ORGS-USERS-003</v>
+      </c>
+      <c r="D1135" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1135" t="str">
+        <v>[ORGS-USERS-003] : Organization-wide owner visibility returns full list → 200</v>
+      </c>
+      <c r="F1135" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1135">
+        <v>2806</v>
+      </c>
+      <c r="H1135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1136" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1136" t="str">
+        <v>ORGS-USERS-005</v>
+      </c>
+      <c r="D1136" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1136" t="str">
+        <v>[ORGS-USERS-005] : Branch-scoped supervisor visibility returns branch users → 200</v>
+      </c>
+      <c r="F1136" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1136">
+        <v>2075</v>
+      </c>
+      <c r="H1136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1137" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1137" t="str">
+        <v>ORGS-USERS-004</v>
+      </c>
+      <c r="D1137" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1137" t="str">
+        <v>[ORGS-USERS-004] : Self-only employee visibility returns own record → 200</v>
+      </c>
+      <c r="F1137" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1137">
+        <v>1611</v>
+      </c>
+      <c r="H1137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1138" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>ORGS-USERS-008</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1138" t="str">
+        <v>[ORGS-USERS-008] : Matching search query returns filtered users → 200</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1138">
+        <v>1705</v>
+      </c>
+      <c r="H1138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1139" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>ORGS-USERS-006</v>
+      </c>
+      <c r="D1139" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1139" t="str">
+        <v>[ORGS-USERS-006] : Protected employee filters do not expose other users → 200</v>
+      </c>
+      <c r="F1139" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1139">
+        <v>2099</v>
+      </c>
+      <c r="H1139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1140" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>ORGS-USERS-007</v>
+      </c>
+      <c r="D1140" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1140" t="str">
+        <v>[ORGS-USERS-007] : Invalid branchId or departmentId filters return 4xx → 4XX</v>
+      </c>
+      <c r="F1140" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1140">
+        <v>1876</v>
+      </c>
+      <c r="H1140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1141" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>ORGS-OPTS-003</v>
+      </c>
+      <c r="D1141" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1141" t="str">
+        <v>[ORGS-OPTS-003] : Owner-selected branch options return successfully → 200</v>
+      </c>
+      <c r="F1141" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1141">
+        <v>3817</v>
+      </c>
+      <c r="H1141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1142" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>ORGS-OPTS-004</v>
+      </c>
+      <c r="D1142" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1142" t="str">
+        <v>[ORGS-OPTS-004] : Employee own-branch options return successfully → 200</v>
+      </c>
+      <c r="F1142" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1142">
+        <v>5002</v>
+      </c>
+      <c r="H1142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1143" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>ORGS-OPTS-005</v>
+      </c>
+      <c r="D1143" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1143" t="str">
+        <v>[ORGS-OPTS-005] : Forbidden employee cross-branch options request is rejected → 4XX</v>
+      </c>
+      <c r="F1143" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1143">
+        <v>4865</v>
+      </c>
+      <c r="H1143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1144" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>ORGS-OPTS-006</v>
+      </c>
+      <c r="D1144" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1144" t="str">
+        <v>[ORGS-OPTS-006] : Forbidden supervisor cross-branch options request is rejected → 4XX</v>
+      </c>
+      <c r="F1144" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1144">
+        <v>4441</v>
+      </c>
+      <c r="H1144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1145" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>ORGS-CREATE-013</v>
+      </c>
+      <c r="D1145" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1145" t="str">
+        <v>[ORGS-CREATE-013] : Mandatory create fields are enforced → 400</v>
+      </c>
+      <c r="F1145" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1145">
+        <v>1773</v>
+      </c>
+      <c r="H1145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1146" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>ORGS-CREATE-014</v>
+      </c>
+      <c r="D1146" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1146" t="str">
+        <v>[ORGS-CREATE-014] : Forbidden OWNER branchRole creation is rejected → 400</v>
+      </c>
+      <c r="F1146" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1146">
+        <v>1887</v>
+      </c>
+      <c r="H1146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1147" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>ORGS-CREATE-015</v>
+      </c>
+      <c r="D1147" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1147" t="str">
+        <v>[ORGS-CREATE-015] : Invalid supervisorOrgUserId for EMPLOYEE target is rejected → 400</v>
+      </c>
+      <c r="F1147" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1147">
+        <v>3138</v>
+      </c>
+      <c r="H1147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v>40a0dc11-a74f-40e0-8791-fa6157a57f3d</v>
+      </c>
+      <c r="B1148" t="str">
+        <v>2026-04-29 20:29:29 NPT</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>ORGS-PATCH-002</v>
+      </c>
+      <c r="D1148" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1148" t="str">
+        <v>[ORGS-PATCH-002] : Missing fullName on patch returns 400 or 422 → 400</v>
+      </c>
+      <c r="F1148" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1148">
+        <v>2155</v>
+      </c>
+      <c r="H1148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1149" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>AUTH-FORGOT-003</v>
+      </c>
+      <c r="D1149" t="str">
+        <v>api/modules/auth/negative/auth.forgot-password.negative.spec.js</v>
+      </c>
+      <c r="E1149" t="str">
+        <v>[AUTH-FORGOT-003] : Missing email returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1149" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1149">
+        <v>1733</v>
+      </c>
+      <c r="H1149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1150" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>AUTH-LOGIN-002</v>
+      </c>
+      <c r="D1150" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1150" t="str">
+        <v>[AUTH-LOGIN-002] : Invalid password returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1150" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1150">
+        <v>1875</v>
+      </c>
+      <c r="H1150" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1151" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>AUTH-LOGIN-003</v>
+      </c>
+      <c r="D1151" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1151" t="str">
+        <v>[AUTH-LOGIN-003] : Unknown email returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1151">
+        <v>328</v>
+      </c>
+      <c r="H1151" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1152" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>AUTH-LOGIN-004</v>
+      </c>
+      <c r="D1152" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1152" t="str">
+        <v>[AUTH-LOGIN-004] : Missing email returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1152" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1152">
+        <v>353</v>
+      </c>
+      <c r="H1152" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1153" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>AUTH-LOGIN-005</v>
+      </c>
+      <c r="D1153" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1153" t="str">
+        <v>[AUTH-LOGIN-005] : Missing password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1153" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1153">
+        <v>339</v>
+      </c>
+      <c r="H1153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1154" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>AUTH-LOGIN-006</v>
+      </c>
+      <c r="D1154" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1154" t="str">
+        <v>[AUTH-LOGIN-006] : Invalid email format returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1154" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1154">
+        <v>301</v>
+      </c>
+      <c r="H1154" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1155" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>AUTH-LOGIN-007</v>
+      </c>
+      <c r="D1155" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1155" t="str">
+        <v>[AUTH-LOGIN-007] : Empty password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1155" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1155">
+        <v>313</v>
+      </c>
+      <c r="H1155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1156" xml:space="preserve">
+      <c r="A1156" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1156" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>AUTH-LOGIN-008</v>
+      </c>
+      <c r="D1156" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1156" t="str">
+        <v>[AUTH-LOGIN-008] : Trimmed email with extra spaces is accepted → 200</v>
+      </c>
+      <c r="F1156" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1156">
+        <v>302</v>
+      </c>
+      <c r="H1156" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 422 — Validation failed.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1157" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1157" t="str">
+        <v>AUTH-LOGIN-009</v>
+      </c>
+      <c r="D1157" t="str">
+        <v>api/modules/auth/negative/auth.login.negative.spec.js</v>
+      </c>
+      <c r="E1157" t="str">
+        <v>[AUTH-LOGIN-009] : Uppercase email is accepted → 200</v>
+      </c>
+      <c r="F1157" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1157">
+        <v>1086</v>
+      </c>
+      <c r="H1157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1158" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1158" t="str">
+        <v>AUTH-PACT-001</v>
+      </c>
+      <c r="D1158" t="str">
+        <v>api/modules/auth/negative/auth.password-action.negative.spec.js</v>
+      </c>
+      <c r="E1158" t="str">
+        <v>[AUTH-PACT-001] : Missing token returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1158" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1158">
+        <v>1666</v>
+      </c>
+      <c r="H1158" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1159" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1159" t="str">
+        <v>AUTH-PACT-002</v>
+      </c>
+      <c r="D1159" t="str">
+        <v>api/modules/auth/negative/auth.password-action.negative.spec.js</v>
+      </c>
+      <c r="E1159" t="str">
+        <v>[AUTH-PACT-002] : Invalid or unknown token returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1159" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1159">
+        <v>363</v>
+      </c>
+      <c r="H1159" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1160" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1160" t="str">
+        <v>AUTH-REFRESH-002</v>
+      </c>
+      <c r="D1160" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1160" t="str">
+        <v>[AUTH-REFRESH-002] : Missing refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1160" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1160">
+        <v>1612</v>
+      </c>
+      <c r="H1160" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1161" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1161" t="str">
+        <v>AUTH-REFRESH-003</v>
+      </c>
+      <c r="D1161" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1161" t="str">
+        <v>[AUTH-REFRESH-003] : Malformed refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1161" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1161">
+        <v>404</v>
+      </c>
+      <c r="H1161" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1162" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1162" t="str">
+        <v>AUTH-REFRESH-004</v>
+      </c>
+      <c r="D1162" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1162" t="str">
+        <v>[AUTH-REFRESH-004] : Unknown refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1162" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1162">
+        <v>320</v>
+      </c>
+      <c r="H1162" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1163" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1163" t="str">
+        <v>AUTH-REFRESH-005</v>
+      </c>
+      <c r="D1163" t="str">
+        <v>api/modules/auth/negative/auth.refresh.negative.spec.js</v>
+      </c>
+      <c r="E1163" t="str">
+        <v>[AUTH-REFRESH-005] : Reused refresh token after rotation returns 401 Unauthorized → 200</v>
+      </c>
+      <c r="F1163" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1163">
+        <v>3348</v>
+      </c>
+      <c r="H1163" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1164" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1164" t="str">
+        <v>AUTH-SENDOTP-002</v>
+      </c>
+      <c r="D1164" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1164" t="str">
+        <v>[AUTH-SENDOTP-002] : Missing loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1164" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1164">
+        <v>1506</v>
+      </c>
+      <c r="H1164" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1165" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1165" t="str">
+        <v>AUTH-SENDOTP-003</v>
+      </c>
+      <c r="D1165" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1165" t="str">
+        <v>[AUTH-SENDOTP-003] : Empty loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1165" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1165">
+        <v>410</v>
+      </c>
+      <c r="H1165" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1166" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1166" t="str">
+        <v>AUTH-SENDOTP-004</v>
+      </c>
+      <c r="D1166" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1166" t="str">
+        <v>[AUTH-SENDOTP-004] : Unsupported SMS method returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1166" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1166">
+        <v>1012</v>
+      </c>
+      <c r="H1166" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1167" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1167" t="str">
+        <v>AUTH-SENDOTP-005</v>
+      </c>
+      <c r="D1167" t="str">
+        <v>api/modules/auth/negative/auth.send-otp.negative.spec.js</v>
+      </c>
+      <c r="E1167" t="str">
+        <v>[AUTH-SENDOTP-005] : Invalid loginAttemptId returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1167" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1167">
+        <v>303</v>
+      </c>
+      <c r="H1167" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1168" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1168" t="str">
+        <v>AUTH-SETPW-001</v>
+      </c>
+      <c r="D1168" t="str">
+        <v>api/modules/auth/negative/auth.set-password.negative.spec.js</v>
+      </c>
+      <c r="E1168" t="str">
+        <v>[AUTH-SETPW-001] : Weak password returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1168" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1168">
+        <v>1593</v>
+      </c>
+      <c r="H1168" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1169" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1169" t="str">
+        <v>AUTH-SETPW-002</v>
+      </c>
+      <c r="D1169" t="str">
+        <v>api/modules/auth/negative/auth.set-password.negative.spec.js</v>
+      </c>
+      <c r="E1169" t="str">
+        <v>[AUTH-SETPW-002] : Mismatched passwords return 400 Bad Request → 400</v>
+      </c>
+      <c r="F1169" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1169">
+        <v>367</v>
+      </c>
+      <c r="H1169" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1170" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1170" t="str">
+        <v>AUTH-VERIFY-002</v>
+      </c>
+      <c r="D1170" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1170" t="str">
+        <v>[AUTH-VERIFY-002] : Missing OTP generation returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1170" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1170">
+        <v>799</v>
+      </c>
+      <c r="H1170" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1171" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1171" t="str">
+        <v>AUTH-VERIFY-003</v>
+      </c>
+      <c r="D1171" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1171" t="str">
+        <v>[AUTH-VERIFY-003] : Invalid OTP returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1171" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1171">
+        <v>1266</v>
+      </c>
+      <c r="H1171" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1172" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1172" t="str">
+        <v>AUTH-VERIFY-004</v>
+      </c>
+      <c r="D1172" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1172" t="str">
+        <v>[AUTH-VERIFY-004] : Missing loginAttemptId returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1172" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1172">
+        <v>328</v>
+      </c>
+      <c r="H1172" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1173" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1173" t="str">
+        <v>AUTH-VERIFY-005</v>
+      </c>
+      <c r="D1173" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1173" t="str">
+        <v>[AUTH-VERIFY-005] : Missing otp returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1173" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1173">
+        <v>1199</v>
+      </c>
+      <c r="H1173" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1174" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1174" t="str">
+        <v>AUTH-VERIFY-006</v>
+      </c>
+      <c r="D1174" t="str">
+        <v>api/modules/auth/negative/auth.verify-otp.negative.spec.js</v>
+      </c>
+      <c r="E1174" t="str">
+        <v>[AUTH-VERIFY-006] : Reused OTP attempt returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1174" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1174">
+        <v>2334</v>
+      </c>
+      <c r="H1174" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1175" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1175" t="str">
+        <v>AUTH-LOGIN-001</v>
+      </c>
+      <c r="D1175" t="str">
+        <v>api/modules/auth/smoke/auth.login.spec.js</v>
+      </c>
+      <c r="E1175" t="str">
+        <v>[AUTH-LOGIN-001] : Valid credentials → OTP challenge → 200</v>
+      </c>
+      <c r="F1175" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1175">
+        <v>709</v>
+      </c>
+      <c r="H1175" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1176" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1176" t="str">
+        <v>AUTH-REFRESH-001</v>
+      </c>
+      <c r="D1176" t="str">
+        <v>api/modules/auth/smoke/auth.refresh.spec.js</v>
+      </c>
+      <c r="E1176" t="str">
+        <v>[AUTH-REFRESH-001] : Successful OTP flow refreshes token with JSON refreshToken → 200</v>
+      </c>
+      <c r="F1176" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1176">
+        <v>3117</v>
+      </c>
+      <c r="H1176" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1177" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1177" t="str">
+        <v>AUTH-SENDOTP-001</v>
+      </c>
+      <c r="D1177" t="str">
+        <v>api/modules/auth/smoke/auth.send-otp.spec.js</v>
+      </c>
+      <c r="E1177" t="str">
+        <v>[AUTH-SENDOTP-001] : Successful login sends OTP with EMAIL method → 200</v>
+      </c>
+      <c r="F1177" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1177">
+        <v>803</v>
+      </c>
+      <c r="H1177" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1178" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1178" t="str">
+        <v>AUTH-VERIFY-001</v>
+      </c>
+      <c r="D1178" t="str">
+        <v>api/modules/auth/smoke/auth.verify-otp.spec.js</v>
+      </c>
+      <c r="E1178" t="str">
+        <v>[AUTH-VERIFY-001] : Successful login-send-otp-verify flow returns tokens → 200</v>
+      </c>
+      <c r="F1178" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1178">
+        <v>1933</v>
+      </c>
+      <c r="H1178" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1179" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1179" t="str">
+        <v>TASKS-BOARD-001</v>
+      </c>
+      <c r="D1179" t="str">
+        <v>api/modules/tasks/negative/tasks.board.negative.spec.js</v>
+      </c>
+      <c r="E1179" t="str">
+        <v>[TASKS-BOARD-001] : Unauthorized board request returns 401</v>
+      </c>
+      <c r="F1179" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1179">
+        <v>317</v>
+      </c>
+      <c r="H1179" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1180" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1180" t="str">
+        <v>TASKS-LIST-002</v>
+      </c>
+      <c r="D1180" t="str">
+        <v>api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+      </c>
+      <c r="E1180" t="str">
+        <v>[TASKS-LIST-002] : Unauthorized tasks list request returns 401 → 401</v>
+      </c>
+      <c r="F1180" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1180">
+        <v>348</v>
+      </c>
+      <c r="H1180" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1181" xml:space="preserve">
+      <c r="A1181" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1181" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1181" t="str">
+        <v>TASKS-LIST-011</v>
+      </c>
+      <c r="D1181" t="str">
+        <v>api/modules/tasks/negative/tasks.list.negative.spec.js</v>
+      </c>
+      <c r="E1181" t="str">
+        <v>[TASKS-LIST-011] : Tasks list rejects pageSize above max (101) → 422 or 400</v>
+      </c>
+      <c r="F1181" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1181">
+        <v>2348</v>
+      </c>
+      <c r="H1181" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBe_x001b_[2m(_x001b_[22m_x001b_[32mexpected_x001b_[39m_x001b_[2m) // Object.is equality_x001b_[22m
+Expected: _x001b_[32m"string"_x001b_[39m
+Received: _x001b_[31m"undefined"_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1182" xml:space="preserve">
+      <c r="A1182" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1182" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1182" t="str">
+        <v>TASKS-ANALYTICS-001</v>
+      </c>
+      <c r="D1182" t="str">
+        <v>api/modules/tasks/smoke/tasks.analytics.spec.js</v>
+      </c>
+      <c r="E1182" t="str">
+        <v>[TASKS-ANALYTICS-001] : Task analytics summary returns success</v>
+      </c>
+      <c r="F1182" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1182">
+        <v>2921</v>
+      </c>
+      <c r="H1182" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 400 — Task not found.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1183" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1183" t="str">
+        <v>TASKS-LIST-006</v>
+      </c>
+      <c r="D1183" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1183" t="str">
+        <v>[TASKS-LIST-006] : Board view task list returns successfully → 2XX</v>
+      </c>
+      <c r="F1183" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1183">
+        <v>2832</v>
+      </c>
+      <c r="H1183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1184" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1184" t="str">
+        <v>TASKS-LIST-007</v>
+      </c>
+      <c r="D1184" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1184" t="str">
+        <v>[TASKS-LIST-007] : Filtered board view with assigneeId returns successfully → 2XX</v>
+      </c>
+      <c r="F1184" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1184">
+        <v>1432</v>
+      </c>
+      <c r="H1184" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1185" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1185" t="str">
+        <v>TASKS-LIST-008</v>
+      </c>
+      <c r="D1185" t="str">
+        <v>api/modules/tasks/smoke/tasks.boardview.spec.js</v>
+      </c>
+      <c r="E1185" t="str">
+        <v>[TASKS-LIST-008] : Task detail endpoint returns selected task payload → 2XX</v>
+      </c>
+      <c r="F1185" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1185">
+        <v>1517</v>
+      </c>
+      <c r="H1185" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1186" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1186" t="str">
+        <v>TASKS-COMMENTS-001</v>
+      </c>
+      <c r="D1186" t="str">
+        <v>api/modules/tasks/smoke/tasks.comments.spec.js</v>
+      </c>
+      <c r="E1186" t="str">
+        <v>[TASKS-COMMENTS-001] : List task comments returns success</v>
+      </c>
+      <c r="F1186" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1186">
+        <v>2870</v>
+      </c>
+      <c r="H1186" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1187" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1187" t="str">
+        <v>TASKS-POST-001</v>
+      </c>
+      <c r="D1187" t="str">
+        <v>api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+      <c r="E1187" t="str">
+        <v>[TASKS-POST-001] : Create branch task returns success with taskId</v>
+      </c>
+      <c r="F1187" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1187">
+        <v>690</v>
+      </c>
+      <c r="H1187" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1188" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1188" t="str">
+        <v>TASKS-PATCH-001</v>
+      </c>
+      <c r="D1188" t="str">
+        <v>api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+      <c r="E1188" t="str">
+        <v>[TASKS-PATCH-001] : Update branch task returns success</v>
+      </c>
+      <c r="F1188" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1188">
+        <v>304</v>
+      </c>
+      <c r="H1188" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1189" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1189" t="str">
+        <v>TASKS-DELETE-001</v>
+      </c>
+      <c r="D1189" t="str">
+        <v>api/modules/tasks/smoke/tasks.crud.spec.js</v>
+      </c>
+      <c r="E1189" t="str">
+        <v>[TASKS-DELETE-001] : Delete branch task returns success</v>
+      </c>
+      <c r="F1189" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1189">
+        <v>310</v>
+      </c>
+      <c r="H1189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1190" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1190" t="str">
+        <v>TASKS-LIST-001</v>
+      </c>
+      <c r="D1190" t="str">
+        <v>api/modules/tasks/smoke/tasks.list.spec.js</v>
+      </c>
+      <c r="E1190" t="str">
+        <v>[TASKS-LIST-001] : Authorized owner lists tasks with pagination and filters → 2XX</v>
+      </c>
+      <c r="F1190" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1190">
+        <v>2366</v>
+      </c>
+      <c r="H1190" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1191" xml:space="preserve">
+      <c r="A1191" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1191" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1191" t="str">
+        <v>TASKS-NOTIF-001</v>
+      </c>
+      <c r="D1191" t="str">
+        <v>api/modules/tasks/smoke/tasks.notifications.spec.js</v>
+      </c>
+      <c r="E1191" t="str">
+        <v>[TASKS-NOTIF-001] : List task notifications returns success</v>
+      </c>
+      <c r="F1191" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1191">
+        <v>1742</v>
+      </c>
+      <c r="H1191" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 422 — Validation failed.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1192" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1192" t="str">
+        <v>TASKS-FILTERS-001</v>
+      </c>
+      <c r="D1192" t="str">
+        <v>api/modules/tasks/smoke/tasks.saved-filters.spec.js</v>
+      </c>
+      <c r="E1192" t="str">
+        <v>[TASKS-FILTERS-001] : List analytics saved filters returns success</v>
+      </c>
+      <c r="F1192" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1192">
+        <v>2732</v>
+      </c>
+      <c r="H1192" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1193" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1193" t="str">
+        <v>TASKS-SETTINGS-001</v>
+      </c>
+      <c r="D1193" t="str">
+        <v>api/modules/tasks/smoke/tasks.settings.spec.js</v>
+      </c>
+      <c r="E1193" t="str">
+        <v>[TASKS-SETTINGS-001] : List org task statuses returns success</v>
+      </c>
+      <c r="F1193" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1193">
+        <v>1566</v>
+      </c>
+      <c r="H1193" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1194" xml:space="preserve">
+      <c r="A1194" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1194" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1194" t="str">
+        <v>TASKS-SUBTREE-001</v>
+      </c>
+      <c r="D1194" t="str">
+        <v>api/modules/tasks/smoke/tasks.subtasks-tree.spec.js</v>
+      </c>
+      <c r="E1194" t="str">
+        <v>[TASKS-SUBTREE-001] : Subtask tree endpoint returns JSON array payload</v>
+      </c>
+      <c r="F1194" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1194">
+        <v>3468</v>
+      </c>
+      <c r="H1194" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: _x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1195" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1195" t="str">
+        <v>ORGS-CREATE-002</v>
+      </c>
+      <c r="D1195" t="str">
+        <v>api/modules/users/negative/users.create.negative.spec.js</v>
+      </c>
+      <c r="E1195" t="str">
+        <v>[ORGS-CREATE-002] : Unauthorized create request returns 401 → 401</v>
+      </c>
+      <c r="F1195" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1195">
+        <v>300</v>
+      </c>
+      <c r="H1195" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1196" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1196" t="str">
+        <v>ORGS-CREATE-003</v>
+      </c>
+      <c r="D1196" t="str">
+        <v>api/modules/users/negative/users.create.negative.spec.js</v>
+      </c>
+      <c r="E1196" t="str">
+        <v>[ORGS-CREATE-003] : Missing email on create returns 422 Validation Error → 422</v>
+      </c>
+      <c r="F1196" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1196">
+        <v>2025</v>
+      </c>
+      <c r="H1196" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1197" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1197" t="str">
+        <v>ORGS-USERS-GET-002</v>
+      </c>
+      <c r="D1197" t="str">
+        <v>api/modules/users/negative/users.get.negative.spec.js</v>
+      </c>
+      <c r="E1197" t="str">
+        <v>[ORGS-USERS-GET-002] : Unauthorized request without Authorization header → 401</v>
+      </c>
+      <c r="F1197" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1197">
+        <v>289</v>
+      </c>
+      <c r="H1197" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1198" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1198" t="str">
+        <v>ORGS-USERS-002</v>
+      </c>
+      <c r="D1198" t="str">
+        <v>api/modules/users/negative/users.list.negative.spec.js</v>
+      </c>
+      <c r="E1198" t="str">
+        <v>[ORGS-USERS-002] : Unauthorized request without Authorization header → 401</v>
+      </c>
+      <c r="F1198" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1198">
+        <v>280</v>
+      </c>
+      <c r="H1198" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1199" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1199" t="str">
+        <v>ORGS-OPTS-002</v>
+      </c>
+      <c r="D1199" t="str">
+        <v>api/modules/users/negative/users.options.negative.spec.js</v>
+      </c>
+      <c r="E1199" t="str">
+        <v>[ORGS-OPTS-002] : Unauthorized request without Authorization → 401</v>
+      </c>
+      <c r="F1199" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1199">
+        <v>276</v>
+      </c>
+      <c r="H1199" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1200" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1200" t="str">
+        <v>ORGS-CREATE-001</v>
+      </c>
+      <c r="D1200" t="str">
+        <v>api/modules/users/smoke/users.create.spec.js</v>
+      </c>
+      <c r="E1200" t="str">
+        <v>[ORGS-CREATE-001] : Authorized owner creates user with minimal body → 2XX</v>
+      </c>
+      <c r="F1200" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1200">
+        <v>2433</v>
+      </c>
+      <c r="H1200" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1201" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1201" t="str">
+        <v>ORGS-USERS-GET-001</v>
+      </c>
+      <c r="D1201" t="str">
+        <v>api/modules/users/smoke/users.get.spec.js</v>
+      </c>
+      <c r="E1201" t="str">
+        <v>[ORGS-USERS-GET-001] : Authorized owner gets caller orgUserId details → 200</v>
+      </c>
+      <c r="F1201" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1201">
+        <v>2962</v>
+      </c>
+      <c r="H1201" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1202" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1202" t="str">
+        <v>ORGS-USERS-001</v>
+      </c>
+      <c r="D1202" t="str">
+        <v>api/modules/users/smoke/users.list.spec.js</v>
+      </c>
+      <c r="E1202" t="str">
+        <v>[ORGS-USERS-001] : Authorized owner lists users with page and limit → 200</v>
+      </c>
+      <c r="F1202" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1202">
+        <v>2858</v>
+      </c>
+      <c r="H1202" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1203" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1203" t="str">
+        <v>ORGS-OPTS-001</v>
+      </c>
+      <c r="D1203" t="str">
+        <v>api/modules/users/smoke/users.options.spec.js</v>
+      </c>
+      <c r="E1203" t="str">
+        <v>[ORGS-OPTS-001] : Authorized supervisor gets options for session branchId → 200</v>
+      </c>
+      <c r="F1203" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1203">
+        <v>4835</v>
+      </c>
+      <c r="H1203" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1204" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1204" t="str">
+        <v>ORGS-PATCH-001</v>
+      </c>
+      <c r="D1204" t="str">
+        <v>api/modules/users/smoke/users.update.flow.spec.js</v>
+      </c>
+      <c r="E1204" t="str">
+        <v>[ORGS-PATCH-001] : Complete owner create-get-patch-get flow validates updates → 2XX</v>
+      </c>
+      <c r="F1204" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1204">
+        <v>3332</v>
+      </c>
+      <c r="H1204" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1205" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1205" t="str">
+        <v>AUTH-LOGIN-010</v>
+      </c>
+      <c r="D1205" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1205" t="str">
+        <v>[AUTH-LOGIN-010] : Valid seeded login succeeds → 200</v>
+      </c>
+      <c r="F1205" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1205">
+        <v>845</v>
+      </c>
+      <c r="H1205" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1206" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1206" t="str">
+        <v>AUTH-LOGIN-011</v>
+      </c>
+      <c r="D1206" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1206" t="str">
+        <v>[AUTH-LOGIN-011] : Uppercase email login succeeds → 200</v>
+      </c>
+      <c r="F1206" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1206">
+        <v>730</v>
+      </c>
+      <c r="H1206" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1207" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1207" t="str">
+        <v>AUTH-LOGIN-012</v>
+      </c>
+      <c r="D1207" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1207" t="str">
+        <v>[AUTH-LOGIN-012] : Wrong password returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1207" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1207">
+        <v>464</v>
+      </c>
+      <c r="H1207" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1208" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1208" t="str">
+        <v>AUTH-LOGIN-013</v>
+      </c>
+      <c r="D1208" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1208" t="str">
+        <v>[AUTH-LOGIN-013] : Unknown email returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1208" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1208">
+        <v>312</v>
+      </c>
+      <c r="H1208" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1209" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1209" t="str">
+        <v>AUTH-SENDOTP-006</v>
+      </c>
+      <c r="D1209" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1209" t="str">
+        <v>[AUTH-SENDOTP-006] : Valid loginAttemptId with EMAIL succeeds → 200</v>
+      </c>
+      <c r="F1209" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1209">
+        <v>767</v>
+      </c>
+      <c r="H1209" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1210" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1210" t="str">
+        <v>AUTH-SENDOTP-007</v>
+      </c>
+      <c r="D1210" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1210" t="str">
+        <v>[AUTH-SENDOTP-007] : Unsupported SMS method returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1210" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1210">
+        <v>784</v>
+      </c>
+      <c r="H1210" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1211" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1211" t="str">
+        <v>AUTH-VERIFY-007</v>
+      </c>
+      <c r="D1211" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1211" t="str">
+        <v>[AUTH-VERIFY-007] : Valid static OTP after send-otp succeeds → 200</v>
+      </c>
+      <c r="F1211" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1211">
+        <v>1867</v>
+      </c>
+      <c r="H1211" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1212" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1212" t="str">
+        <v>AUTH-VERIFY-008</v>
+      </c>
+      <c r="D1212" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1212" t="str">
+        <v>[AUTH-VERIFY-008] : Premature verify before send-otp returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1212" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1212">
+        <v>1102</v>
+      </c>
+      <c r="H1212" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1213" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1213" t="str">
+        <v>AUTH-VERIFY-009</v>
+      </c>
+      <c r="D1213" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1213" t="str">
+        <v>[AUTH-VERIFY-009] : Wrong OTP returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1213" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1213">
+        <v>1330</v>
+      </c>
+      <c r="H1213" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1214" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1214" t="str">
+        <v>AUTH-VERIFY-010</v>
+      </c>
+      <c r="D1214" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1214" t="str">
+        <v>[AUTH-VERIFY-010] : Double verify on same loginAttemptId returns 400 Bad Request → 400</v>
+      </c>
+      <c r="F1214" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1214">
+        <v>2660</v>
+      </c>
+      <c r="H1214" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1215" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1215" t="str">
+        <v>AUTH-REFRESH-006</v>
+      </c>
+      <c r="D1215" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1215" t="str">
+        <v>[AUTH-REFRESH-006] : Valid body refreshToken refresh succeeds → 200</v>
+      </c>
+      <c r="F1215" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1215">
+        <v>3096</v>
+      </c>
+      <c r="H1215" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1216" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1216" t="str">
+        <v>AUTH-REFRESH-007</v>
+      </c>
+      <c r="D1216" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1216" t="str">
+        <v>[AUTH-REFRESH-007] : Valid cookie-only refresh_token succeeds → 200</v>
+      </c>
+      <c r="F1216" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1216">
+        <v>2472</v>
+      </c>
+      <c r="H1216" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1217" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1217" t="str">
+        <v>AUTH-REFRESH-008</v>
+      </c>
+      <c r="D1217" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1217" t="str">
+        <v>[AUTH-REFRESH-008] : Malformed refresh token returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1217" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1217">
+        <v>353</v>
+      </c>
+      <c r="H1217" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1218" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1218" t="str">
+        <v>MISC-PROT-001</v>
+      </c>
+      <c r="D1218" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1218" t="str">
+        <v>[MISC-PROT-001] : Invalid JWT on protected GET returns 401 Unauthorized → 401</v>
+      </c>
+      <c r="F1218" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1218">
+        <v>297</v>
+      </c>
+      <c r="H1218" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1219" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1219" t="str">
+        <v>AUTH-VERIFY-011</v>
+      </c>
+      <c r="D1219" t="str">
+        <v>api/regression/qa-auth-matrix.spec.js</v>
+      </c>
+      <c r="E1219" t="str">
+        <v>[AUTH-VERIFY-011] : Valid tier-3 member verify includes branch data → 200</v>
+      </c>
+      <c r="F1219" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1219">
+        <v>1917</v>
+      </c>
+      <c r="H1219" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1220" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1220" t="str">
+        <v>TASKS-LIST-003</v>
+      </c>
+      <c r="D1220" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1220" t="str">
+        <v>[TASKS-LIST-003] : Owner branch tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1220" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1220">
+        <v>2380</v>
+      </c>
+      <c r="H1220" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1221" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1221" t="str">
+        <v>TASKS-LIST-004</v>
+      </c>
+      <c r="D1221" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1221" t="str">
+        <v>[TASKS-LIST-004] : Supervisor branch tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1221" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1221">
+        <v>2216</v>
+      </c>
+      <c r="H1221" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1222" xml:space="preserve">
+      <c r="A1222" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1222" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1222" t="str">
+        <v>TASKS-LIST-005</v>
+      </c>
+      <c r="D1222" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1222" t="str">
+        <v>[TASKS-LIST-005] : Employee scoped tasks list returns successfully → 2XX</v>
+      </c>
+      <c r="F1222" t="str">
+        <v>failed</v>
+      </c>
+      <c r="G1222">
+        <v>1934</v>
+      </c>
+      <c r="H1222" t="str" xml:space="preserve">
+        <v xml:space="preserve">Error: Expected 2xx, got HTTP 401 — Authentication required.
+_x001b_[2mexpect(_x001b_[22m_x001b_[31mreceived_x001b_[39m_x001b_[2m)._x001b_[22mtoBeTruthy_x001b_[2m()_x001b_[22m
+Received: _x001b_[31mfalse_x001b_[39m</v>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1223" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1223" t="str">
+        <v>TASKS-LIST-009</v>
+      </c>
+      <c r="D1223" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1223" t="str">
+        <v>[TASKS-LIST-009] : Forbidden supervisor cross-branch task list request is rejected → 4XX</v>
+      </c>
+      <c r="F1223" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1223">
+        <v>7260</v>
+      </c>
+      <c r="H1223" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1224" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1224" t="str">
+        <v>TASKS-LIST-010</v>
+      </c>
+      <c r="D1224" t="str">
+        <v>api/regression/tasks.list.access.spec.js</v>
+      </c>
+      <c r="E1224" t="str">
+        <v>[TASKS-LIST-010] : Forbidden employee cross-branch task list request is rejected → 4XX</v>
+      </c>
+      <c r="F1224" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1224">
+        <v>5809</v>
+      </c>
+      <c r="H1224" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1225" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1225" t="str">
+        <v>ORGS-PATCH-004</v>
+      </c>
+      <c r="D1225" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1225" t="str">
+        <v>[ORGS-PATCH-004] : Authorized owner updates user in own branch → 200</v>
+      </c>
+      <c r="F1225" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1225">
+        <v>1977</v>
+      </c>
+      <c r="H1225" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1226" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1226" t="str">
+        <v>ORGS-PATCH-005</v>
+      </c>
+      <c r="D1226" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1226" t="str">
+        <v>[ORGS-PATCH-005] : Authorized supervisor updates user in own branch → 200</v>
+      </c>
+      <c r="F1226" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1226">
+        <v>1863</v>
+      </c>
+      <c r="H1226" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1227" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1227" t="str">
+        <v>ORGS-CREATE-004</v>
+      </c>
+      <c r="D1227" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1227" t="str">
+        <v>[ORGS-CREATE-004] : Forbidden employee create attempt is blocked → 401</v>
+      </c>
+      <c r="F1227" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1227">
+        <v>2201</v>
+      </c>
+      <c r="H1227" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1228" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1228" t="str">
+        <v>ORGS-CREATE-016</v>
+      </c>
+      <c r="D1228" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1228" t="str">
+        <v>[ORGS-CREATE-016] : Missing required create fields return 422 Validation Error → 422</v>
+      </c>
+      <c r="F1228" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1228">
+        <v>1822</v>
+      </c>
+      <c r="H1228" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1229" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1229" t="str">
+        <v>ORGS-CREATE-006</v>
+      </c>
+      <c r="D1229" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1229" t="str">
+        <v>[ORGS-CREATE-006] : Invalid supervisor branch override is rejected → 400</v>
+      </c>
+      <c r="F1229" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1229">
+        <v>2370</v>
+      </c>
+      <c r="H1229" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1230" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1230" t="str">
+        <v>ORGS-PATCH-010</v>
+      </c>
+      <c r="D1230" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1230" t="str">
+        <v>[ORGS-PATCH-010] : Forbidden supervisor branchRole change is rejected → 400</v>
+      </c>
+      <c r="F1230" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1230">
+        <v>2410</v>
+      </c>
+      <c r="H1230" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1231" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1231" t="str">
+        <v>ORGS-CREATE-008</v>
+      </c>
+      <c r="D1231" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1231" t="str">
+        <v>[ORGS-CREATE-008] : Duplicate membership in same org/branch is rejected → 400</v>
+      </c>
+      <c r="F1231" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1231">
+        <v>2067</v>
+      </c>
+      <c r="H1231" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1232" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1232" t="str">
+        <v>ORGS-CREATE-009</v>
+      </c>
+      <c r="D1232" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1232" t="str">
+        <v>[ORGS-CREATE-009] : Invalid department id is rejected → 400</v>
+      </c>
+      <c r="F1232" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1232">
+        <v>1952</v>
+      </c>
+      <c r="H1232" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1233" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1233" t="str">
+        <v>ORGS-CREATE-010</v>
+      </c>
+      <c r="D1233" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1233" t="str">
+        <v>[ORGS-CREATE-010] : Invalid supervisorOrgUserId is rejected → 400</v>
+      </c>
+      <c r="F1233" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1233">
+        <v>2251</v>
+      </c>
+      <c r="H1233" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1234" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1234" t="str">
+        <v>ORGS-CREATE-011</v>
+      </c>
+      <c r="D1234" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1234" t="str">
+        <v>[ORGS-CREATE-011] : Forbidden supervisor payroll fields are rejected → 400</v>
+      </c>
+      <c r="F1234" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1234">
+        <v>1555</v>
+      </c>
+      <c r="H1234" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1235" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1235" t="str">
+        <v>ORGS-CREATE-005</v>
+      </c>
+      <c r="D1235" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1235" t="str">
+        <v>[ORGS-CREATE-005] : Valid supervisor creates employee in own branch → 2XX</v>
+      </c>
+      <c r="F1235" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1235">
+        <v>2084</v>
+      </c>
+      <c r="H1235" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1236" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1236" t="str">
+        <v>ORGS-PATCH-006</v>
+      </c>
+      <c r="D1236" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1236" t="str">
+        <v>[ORGS-PATCH-006] : Forbidden supervisor NI update is rejected → 400</v>
+      </c>
+      <c r="F1236" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1236">
+        <v>1708</v>
+      </c>
+      <c r="H1236" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1237" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1237" t="str">
+        <v>ORGS-PATCH-007</v>
+      </c>
+      <c r="D1237" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1237" t="str">
+        <v>[ORGS-PATCH-007] : Forbidden supervisor share code update is rejected → 400</v>
+      </c>
+      <c r="F1237" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1237">
+        <v>1820</v>
+      </c>
+      <c r="H1237" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1238" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1238" t="str">
+        <v>ORGS-PATCH-009</v>
+      </c>
+      <c r="D1238" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1238" t="str">
+        <v>[ORGS-PATCH-009] : Forbidden supervisor tax ID update is rejected → 400</v>
+      </c>
+      <c r="F1238" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1238">
+        <v>1708</v>
+      </c>
+      <c r="H1238" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1239" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1239" t="str">
+        <v>ORGS-CREATE-007</v>
+      </c>
+      <c r="D1239" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1239" t="str">
+        <v>[ORGS-CREATE-007] : Forbidden supervisor-created SUPERVISOR role is rejected → 400</v>
+      </c>
+      <c r="F1239" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1239">
+        <v>1741</v>
+      </c>
+      <c r="H1239" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1240" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1240" t="str">
+        <v>ORGS-PATCH-008</v>
+      </c>
+      <c r="D1240" t="str">
+        <v>api/regression/users.create.rules.spec.js</v>
+      </c>
+      <c r="E1240" t="str">
+        <v>[ORGS-PATCH-008] : Forbidden supervisor module permission update is rejected → 400</v>
+      </c>
+      <c r="F1240" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1240">
+        <v>1713</v>
+      </c>
+      <c r="H1240" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1241" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1241" t="str">
+        <v>ORGS-USERS-GET-003</v>
+      </c>
+      <c r="D1241" t="str">
+        <v>api/regression/users.get.access.spec.js</v>
+      </c>
+      <c r="E1241" t="str">
+        <v>[ORGS-USERS-GET-003] : Forbidden employee access to another user detail is rejected → 4XX</v>
+      </c>
+      <c r="F1241" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1241">
+        <v>4561</v>
+      </c>
+      <c r="H1241" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1242" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1242" t="str">
+        <v>ORGS-USERS-GET-004</v>
+      </c>
+      <c r="D1242" t="str">
+        <v>api/regression/users.get.access.spec.js</v>
+      </c>
+      <c r="E1242" t="str">
+        <v>[ORGS-USERS-GET-004] : Forbidden supervisor access to out-of-scope user detail is rejected → 4XX</v>
+      </c>
+      <c r="F1242" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1242">
+        <v>4787</v>
+      </c>
+      <c r="H1242" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1243" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1243" t="str">
+        <v>ORGS-PATCH-003</v>
+      </c>
+      <c r="D1243" t="str">
+        <v>api/regression/users.inactive-access.spec.js</v>
+      </c>
+      <c r="E1243" t="str">
+        <v>[ORGS-PATCH-003] : Inactive employee status blocks new session login → 200</v>
+      </c>
+      <c r="F1243" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1243">
+        <v>4690</v>
+      </c>
+      <c r="H1243" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1244" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1244" t="str">
+        <v>ORGS-USERS-003</v>
+      </c>
+      <c r="D1244" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1244" t="str">
+        <v>[ORGS-USERS-003] : Organization-wide owner visibility returns full list → 200</v>
+      </c>
+      <c r="F1244" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1244">
+        <v>2248</v>
+      </c>
+      <c r="H1244" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1245" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1245" t="str">
+        <v>ORGS-USERS-005</v>
+      </c>
+      <c r="D1245" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1245" t="str">
+        <v>[ORGS-USERS-005] : Branch-scoped supervisor visibility returns branch users → 200</v>
+      </c>
+      <c r="F1245" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1245">
+        <v>2093</v>
+      </c>
+      <c r="H1245" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1246" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1246" t="str">
+        <v>ORGS-USERS-004</v>
+      </c>
+      <c r="D1246" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1246" t="str">
+        <v>[ORGS-USERS-004] : Self-only employee visibility returns own record → 200</v>
+      </c>
+      <c r="F1246" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1246">
+        <v>2856</v>
+      </c>
+      <c r="H1246" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1247" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1247" t="str">
+        <v>ORGS-USERS-008</v>
+      </c>
+      <c r="D1247" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1247" t="str">
+        <v>[ORGS-USERS-008] : Matching search query returns filtered users → 200</v>
+      </c>
+      <c r="F1247" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1247">
+        <v>2261</v>
+      </c>
+      <c r="H1247" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1248" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1248" t="str">
+        <v>ORGS-USERS-006</v>
+      </c>
+      <c r="D1248" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1248" t="str">
+        <v>[ORGS-USERS-006] : Protected employee filters do not expose other users → 200</v>
+      </c>
+      <c r="F1248" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1248">
+        <v>2154</v>
+      </c>
+      <c r="H1248" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1249" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1249" t="str">
+        <v>ORGS-USERS-007</v>
+      </c>
+      <c r="D1249" t="str">
+        <v>api/regression/users.list.visibility.spec.js</v>
+      </c>
+      <c r="E1249" t="str">
+        <v>[ORGS-USERS-007] : Invalid branchId or departmentId filters return 4xx → 4XX</v>
+      </c>
+      <c r="F1249" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1249">
+        <v>2029</v>
+      </c>
+      <c r="H1249" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1250" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1250" t="str">
+        <v>ORGS-OPTS-003</v>
+      </c>
+      <c r="D1250" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1250" t="str">
+        <v>[ORGS-OPTS-003] : Owner-selected branch options return successfully → 200</v>
+      </c>
+      <c r="F1250" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1250">
+        <v>5336</v>
+      </c>
+      <c r="H1250" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1251" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1251" t="str">
+        <v>ORGS-OPTS-004</v>
+      </c>
+      <c r="D1251" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1251" t="str">
+        <v>[ORGS-OPTS-004] : Employee own-branch options return successfully → 200</v>
+      </c>
+      <c r="F1251" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1251">
+        <v>4397</v>
+      </c>
+      <c r="H1251" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1252" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1252" t="str">
+        <v>ORGS-OPTS-005</v>
+      </c>
+      <c r="D1252" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1252" t="str">
+        <v>[ORGS-OPTS-005] : Forbidden employee cross-branch options request is rejected → 4XX</v>
+      </c>
+      <c r="F1252" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1252">
+        <v>5891</v>
+      </c>
+      <c r="H1252" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1253" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1253" t="str">
+        <v>ORGS-OPTS-006</v>
+      </c>
+      <c r="D1253" t="str">
+        <v>api/regression/users.options.access.spec.js</v>
+      </c>
+      <c r="E1253" t="str">
+        <v>[ORGS-OPTS-006] : Forbidden supervisor cross-branch options request is rejected → 4XX</v>
+      </c>
+      <c r="F1253" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1253">
+        <v>4823</v>
+      </c>
+      <c r="H1253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1254" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1254" t="str">
+        <v>ORGS-CREATE-013</v>
+      </c>
+      <c r="D1254" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1254" t="str">
+        <v>[ORGS-CREATE-013] : Mandatory create fields are enforced → 400</v>
+      </c>
+      <c r="F1254" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1254">
+        <v>2297</v>
+      </c>
+      <c r="H1254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1255" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1255" t="str">
+        <v>ORGS-CREATE-014</v>
+      </c>
+      <c r="D1255" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1255" t="str">
+        <v>[ORGS-CREATE-014] : Forbidden OWNER branchRole creation is rejected → 400</v>
+      </c>
+      <c r="F1255" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1255">
+        <v>2154</v>
+      </c>
+      <c r="H1255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1256" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1256" t="str">
+        <v>ORGS-CREATE-015</v>
+      </c>
+      <c r="D1256" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1256" t="str">
+        <v>[ORGS-CREATE-015] : Invalid supervisorOrgUserId for EMPLOYEE target is rejected → 400</v>
+      </c>
+      <c r="F1256" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1256">
+        <v>3657</v>
+      </c>
+      <c r="H1256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="str">
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
+      </c>
+      <c r="B1257" t="str">
+        <v>2026-05-04 23:03:25 NPT</v>
+      </c>
+      <c r="C1257" t="str">
+        <v>ORGS-PATCH-002</v>
+      </c>
+      <c r="D1257" t="str">
+        <v>api/regression/users.profile.validation.spec.js</v>
+      </c>
+      <c r="E1257" t="str">
+        <v>[ORGS-PATCH-002] : Missing fullName on patch returns 400 or 422 → 400</v>
+      </c>
+      <c r="F1257" t="str">
+        <v>passed</v>
+      </c>
+      <c r="G1257">
+        <v>2374</v>
+      </c>
+      <c r="H1257" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H1050"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1257"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -32145,7 +38820,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B2">
-        <v>105</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -32153,7 +38828,7 @@
         <v>Latest Passed</v>
       </c>
       <c r="B3">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4">
@@ -32161,7 +38836,7 @@
         <v>Latest Failed</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -32177,7 +38852,7 @@
         <v>Latest Run ID</v>
       </c>
       <c r="B6" t="str">
-        <v>7454dde4-840f-4a80-90d2-75cc905ab992</v>
+        <v>9ab7cfcc-f608-4e98-aa39-67eeb3c43e9d</v>
       </c>
     </row>
     <row r="7">
@@ -32185,7 +38860,7 @@
         <v>Latest Run Timestamp</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-29T14:38:30.352Z</v>
+        <v>2026-05-04 23:03:25 NPT</v>
       </c>
     </row>
     <row r="8">
@@ -32193,7 +38868,7 @@
         <v>Raw Run Rows</v>
       </c>
       <c r="B8">
-        <v>1049</v>
+        <v>1256</v>
       </c>
     </row>
   </sheetData>
